--- a/المخزن.xlsx
+++ b/المخزن.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G218"/>
+  <dimension ref="A1:G220"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -4753,7 +4753,7 @@
         <v>444</v>
       </c>
       <c r="D218" t="str">
-        <v>فوشيا</v>
+        <v>سوت وسط حوض (فوشيا)</v>
       </c>
       <c r="E218" t="str">
         <v/>
@@ -4765,9 +4765,49 @@
         <v>0</v>
       </c>
     </row>
+    <row r="219">
+      <c r="B219">
+        <v>5030</v>
+      </c>
+      <c r="C219">
+        <v>442</v>
+      </c>
+      <c r="D219" t="str">
+        <v>سوت وسط حوض (اسود)</v>
+      </c>
+      <c r="E219" t="str">
+        <v>بناتي</v>
+      </c>
+      <c r="F219">
+        <v>0</v>
+      </c>
+      <c r="G219">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="220">
+      <c r="B220">
+        <v>5030</v>
+      </c>
+      <c r="C220">
+        <v>443</v>
+      </c>
+      <c r="D220" t="str">
+        <v>سوت وسط حوض (بني فاتح)</v>
+      </c>
+      <c r="E220" t="str">
+        <v>بناتي</v>
+      </c>
+      <c r="F220">
+        <v>0</v>
+      </c>
+      <c r="G220">
+        <v>0</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G218"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:G220"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/المخزن.xlsx
+++ b/المخزن.xlsx
@@ -1,41 +1,396 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\HappyBoy\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37FE9C25-EA69-4941-9F09-849461A6373C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <bookViews>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+  </bookViews>
   <sheets>
     <sheet name="Sheet2" sheetId="1" r:id="rId1"/>
   </sheets>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
-<file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
-  <metadataTypes count="1">
-    <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
-  </metadataTypes>
-  <futureMetadata name="XLDAPR" count="1">
-    <bk>
-      <extLst>
-        <ext uri="{bdbb8cdc-fa1e-496e-a857-3c3f30c029c3}">
-          <xda:dynamicArrayProperties fDynamic="1" fCollapsed="0"/>
-        </ext>
-      </extLst>
-    </bk>
-  </futureMetadata>
-  <cellMetadata count="1">
-    <bk>
-      <rc t="1" v="0"/>
-    </bk>
-  </cellMetadata>
-</metadata>
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="442" uniqueCount="116">
+  <si>
+    <t>كود الموديل</t>
+  </si>
+  <si>
+    <t>الباركود</t>
+  </si>
+  <si>
+    <t>التصنيف</t>
+  </si>
+  <si>
+    <t>التصنيف2</t>
+  </si>
+  <si>
+    <t>عدد الثريهات</t>
+  </si>
+  <si>
+    <t>عدد القطع</t>
+  </si>
+  <si>
+    <t>ترنج اولادى (منت)</t>
+  </si>
+  <si>
+    <t>بيبى ولد</t>
+  </si>
+  <si>
+    <t>ترنج اولادى (رمادى)</t>
+  </si>
+  <si>
+    <t>ترنج اولادى (انديجو)</t>
+  </si>
+  <si>
+    <t>ترنج اولادى(اسود)</t>
+  </si>
+  <si>
+    <t>ترنج اولادى(رمادى)</t>
+  </si>
+  <si>
+    <t>نرنج اولادى (انديجو)</t>
+  </si>
+  <si>
+    <t>ترنج اولادى ( اسود)</t>
+  </si>
+  <si>
+    <t>ترنج اولادى (كافيه)</t>
+  </si>
+  <si>
+    <t>ترنج اولادى (شانيه)</t>
+  </si>
+  <si>
+    <t>ترنج اولادى( شاركول)</t>
+  </si>
+  <si>
+    <t>ترنج اولادى(انديجو)</t>
+  </si>
+  <si>
+    <t>ترنج اولادى(تفاحى)</t>
+  </si>
+  <si>
+    <t>ترنج اولادى(بيج)</t>
+  </si>
+  <si>
+    <t>ترنج اولادى(اصفر)</t>
+  </si>
+  <si>
+    <t>ترنج اولادى(اورانج)</t>
+  </si>
+  <si>
+    <t>ترنج اولادى(اخضر)</t>
+  </si>
+  <si>
+    <t>ترنج اولادى (مسطرده)</t>
+  </si>
+  <si>
+    <t>ترنج اولادى ( احمر)</t>
+  </si>
+  <si>
+    <t>ترنج اولادى(هافان)</t>
+  </si>
+  <si>
+    <t>ترنج اولادى(كافيه)</t>
+  </si>
+  <si>
+    <t>ترنج اولادى(مسطرده)</t>
+  </si>
+  <si>
+    <t>ترنج اولادى (تفاحى)</t>
+  </si>
+  <si>
+    <t>ترنج اولادى (اورانج)</t>
+  </si>
+  <si>
+    <t>ترنج اولادى (بيج)</t>
+  </si>
+  <si>
+    <t>ترنج اولادى (بيطخى)</t>
+  </si>
+  <si>
+    <t>ترنج اولادى (زيتونى)</t>
+  </si>
+  <si>
+    <t>ترنج اولادى(شاركول)</t>
+  </si>
+  <si>
+    <t>ترنج اولادى( اسود)</t>
+  </si>
+  <si>
+    <t>ترنج اولادى(زيتى)</t>
+  </si>
+  <si>
+    <t>تر نج اولادى ( بستاج)</t>
+  </si>
+  <si>
+    <t>ترنج اولادى(ابيض)</t>
+  </si>
+  <si>
+    <t>ترنج اولادى ( كريمى)</t>
+  </si>
+  <si>
+    <t>ترنج اولادى(منت)</t>
+  </si>
+  <si>
+    <t>نرنج اولادى ( اورانج)</t>
+  </si>
+  <si>
+    <t>ترنج اولادى (طوبى)</t>
+  </si>
+  <si>
+    <t>ترنج اولادى (كشمير )</t>
+  </si>
+  <si>
+    <t>ترنج اولادى( زيتونى)</t>
+  </si>
+  <si>
+    <t>ترنج اولادى(احمر)</t>
+  </si>
+  <si>
+    <t>وسط ولد</t>
+  </si>
+  <si>
+    <t>ترنج اولادى (بنى)</t>
+  </si>
+  <si>
+    <t>ترنج اولادى(بطيخى)</t>
+  </si>
+  <si>
+    <t>ترنج اولادى (جيشى)</t>
+  </si>
+  <si>
+    <t>ترنج اولادى(زيتونى)</t>
+  </si>
+  <si>
+    <t>ترنج اولادى( اورانج)</t>
+  </si>
+  <si>
+    <t>ترنج اولادى(شانيه)</t>
+  </si>
+  <si>
+    <t>محير ولد</t>
+  </si>
+  <si>
+    <t>محبر ولد</t>
+  </si>
+  <si>
+    <t>ترنج اولادى (هافان)</t>
+  </si>
+  <si>
+    <t>ترنج اولادى(جيشى)</t>
+  </si>
+  <si>
+    <t>نرنج اولادى (كافيه)</t>
+  </si>
+  <si>
+    <t>ترنج اولادى (شاركول)</t>
+  </si>
+  <si>
+    <t>ترنج اولادى (اسود)</t>
+  </si>
+  <si>
+    <t>ترنج اولادى (احمر)</t>
+  </si>
+  <si>
+    <t>ترنج اولادى( هافان)</t>
+  </si>
+  <si>
+    <t>ترنج بناتى (انديجو)</t>
+  </si>
+  <si>
+    <t>بيبى بنت</t>
+  </si>
+  <si>
+    <t>ترنج بناتى(موف)</t>
+  </si>
+  <si>
+    <t>ترنج بناتى ( رمادى)</t>
+  </si>
+  <si>
+    <t>ترنج بناتى(كافيه)</t>
+  </si>
+  <si>
+    <t>بيبي بنت</t>
+  </si>
+  <si>
+    <t>ترنج بناتى (ابيض)</t>
+  </si>
+  <si>
+    <t>ترنج بناتى (منت)</t>
+  </si>
+  <si>
+    <t>ترنج بناتى (برجاندى)</t>
+  </si>
+  <si>
+    <t>ترنج بناتى (اوف ويت)</t>
+  </si>
+  <si>
+    <t>ترنج بناتى(ابيض)</t>
+  </si>
+  <si>
+    <t>ترنج بناتى(رمادى)</t>
+  </si>
+  <si>
+    <t>ترنج بناتى (لبنى)</t>
+  </si>
+  <si>
+    <t>ترنج بناتى(فوشيا)</t>
+  </si>
+  <si>
+    <t>ترنج بناتى(بستاج)</t>
+  </si>
+  <si>
+    <t>ترنج بناتى (سميون)</t>
+  </si>
+  <si>
+    <t>ترنج بناتى (اصفر)</t>
+  </si>
+  <si>
+    <t>ترنج بناتى (روز)</t>
+  </si>
+  <si>
+    <t>ترنج بناتى( تفاحى)</t>
+  </si>
+  <si>
+    <t>ترنج بناتى(سميون)</t>
+  </si>
+  <si>
+    <t>ترنج بناتى(اصفر)</t>
+  </si>
+  <si>
+    <t>ترنج بناتى(روز)</t>
+  </si>
+  <si>
+    <t>ترنج بناتى (موف)</t>
+  </si>
+  <si>
+    <t>ترنج بناتى(بيج)</t>
+  </si>
+  <si>
+    <t>ترنج بناتى ( تفاحى)</t>
+  </si>
+  <si>
+    <t>ترنج بناتى ( بدى روز)</t>
+  </si>
+  <si>
+    <t>ترنج بناتى (طوبى)</t>
+  </si>
+  <si>
+    <t>وسط بنت</t>
+  </si>
+  <si>
+    <t>ترنج بناتى (كشمير)</t>
+  </si>
+  <si>
+    <t>ترنج بناتى (اسود)</t>
+  </si>
+  <si>
+    <t>ترنج بناتى (بيج)</t>
+  </si>
+  <si>
+    <t>ترنج بناتى ( كشمير)</t>
+  </si>
+  <si>
+    <t>ترنج بناتى ( انديجو)</t>
+  </si>
+  <si>
+    <t>ترنج بناتى (كمونى)</t>
+  </si>
+  <si>
+    <t>ترنج بناتى ( برجندى)</t>
+  </si>
+  <si>
+    <t>ترنج بناتى ( كافيه)</t>
+  </si>
+  <si>
+    <t>ترنج بناتى ( موف)</t>
+  </si>
+  <si>
+    <t>ترنج بناتى (فوشيا)</t>
+  </si>
+  <si>
+    <t>ترنج بناتى (اكوا)</t>
+  </si>
+  <si>
+    <t>ترنج بناتى (بسستاج)</t>
+  </si>
+  <si>
+    <t>ترنج بناتى(اكوا)</t>
+  </si>
+  <si>
+    <t>ترنج بناتى(برجاندى)</t>
+  </si>
+  <si>
+    <t>ترنج بناتى( سميون)</t>
+  </si>
+  <si>
+    <t>ترنج بناتى ( اصفر)</t>
+  </si>
+  <si>
+    <t>محير بنت</t>
+  </si>
+  <si>
+    <t>ترنج بناتى (رمادى)</t>
+  </si>
+  <si>
+    <t>ترنج بناتى ( ابيض)</t>
+  </si>
+  <si>
+    <t>ترنج بناتى ( كمونى)</t>
+  </si>
+  <si>
+    <t>ترنج بناتى( ابيض)</t>
+  </si>
+  <si>
+    <t>ترنج بناتى( بستاج)</t>
+  </si>
+  <si>
+    <t>سوت وسط حوض (فوشيا)</t>
+  </si>
+  <si>
+    <t/>
+  </si>
+  <si>
+    <t>سوت وسط حوض (اسود)</t>
+  </si>
+  <si>
+    <t>بناتي</t>
+  </si>
+  <si>
+    <t>سوت وسط حوض (بني فاتح)</t>
+  </si>
+</sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:vt="http://schemas.openxmlformats.org/officeDocument/2006/docPropsVTypes">
-  <numFmts count="1">
-    <numFmt numFmtId="56" formatCode="&quot;上午/下午 &quot;hh&quot;時&quot;mm&quot;分&quot;ss&quot;秒 &quot;"/>
-  </numFmts>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -72,13 +427,21 @@
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -116,7 +479,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -188,7 +551,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -220,16 +583,20 @@
           <a:gsLst>
             <a:gs pos="0">
               <a:schemeClr val="phClr">
-                <a:tint val="100000"/>
-                <a:shade val="100000"/>
+                <a:shade val="51000"/>
+                <a:satMod val="130000"/>
+              </a:schemeClr>
+            </a:gs>
+            <a:gs pos="80000">
+              <a:schemeClr val="phClr">
+                <a:shade val="93000"/>
                 <a:satMod val="130000"/>
               </a:schemeClr>
             </a:gs>
             <a:gs pos="100000">
               <a:schemeClr val="phClr">
-                <a:tint val="50000"/>
-                <a:shade val="100000"/>
-                <a:satMod val="350000"/>
+                <a:shade val="94000"/>
+                <a:satMod val="135000"/>
               </a:schemeClr>
             </a:gs>
           </a:gsLst>
@@ -351,94 +718,58 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:spDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="3">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </a:style>
-    </a:spDef>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G220"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="B1:G220"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="8.59765625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.69921875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.69921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.69921875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.09765625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="str">
-        <v>__EMPTY</v>
-      </c>
-      <c r="B1" t="str">
-        <v>كود الموديل</v>
-      </c>
-      <c r="C1" t="str">
-        <v>الباركود</v>
-      </c>
-      <c r="D1" t="str">
-        <v>التصنيف</v>
-      </c>
-      <c r="E1" t="str">
-        <v>التصنيف2</v>
-      </c>
-      <c r="F1" t="str">
-        <v>عدد الثريهات</v>
-      </c>
-      <c r="G1" t="str">
-        <v>عدد القطع</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2">
-        <v>40246</v>
-      </c>
-    </row>
-    <row r="3">
+    <row r="1" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E1" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="2:7" ht="15.6" x14ac:dyDescent="0.3"/>
+    <row r="3" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B3">
         <v>5</v>
       </c>
       <c r="C3">
         <v>28</v>
       </c>
-      <c r="D3" t="str">
-        <v>ترنج اولادى (منت)</v>
-      </c>
-      <c r="E3" t="str">
-        <v>بيبى ولد</v>
+      <c r="D3" t="s">
+        <v>6</v>
+      </c>
+      <c r="E3" t="s">
+        <v>7</v>
       </c>
       <c r="F3">
         <v>49.75</v>
@@ -447,18 +778,18 @@
         <v>199</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B4">
         <v>5</v>
       </c>
       <c r="C4">
         <v>29</v>
       </c>
-      <c r="D4" t="str">
-        <v>ترنج اولادى (رمادى)</v>
-      </c>
-      <c r="E4" t="str">
-        <v>بيبى ولد</v>
+      <c r="D4" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" t="s">
+        <v>7</v>
       </c>
       <c r="F4">
         <v>50</v>
@@ -467,18 +798,18 @@
         <v>200</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B5">
         <v>5</v>
       </c>
       <c r="C5">
         <v>30</v>
       </c>
-      <c r="D5" t="str">
-        <v>ترنج اولادى (انديجو)</v>
-      </c>
-      <c r="E5" t="str">
-        <v>بيبى ولد</v>
+      <c r="D5" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" t="s">
+        <v>7</v>
       </c>
       <c r="F5">
         <v>49</v>
@@ -487,18 +818,18 @@
         <v>196</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B6">
         <v>10</v>
       </c>
       <c r="C6">
         <v>31</v>
       </c>
-      <c r="D6" t="str">
-        <v>ترنج اولادى(اسود)</v>
-      </c>
-      <c r="E6" t="str">
-        <v>بيبى ولد</v>
+      <c r="D6" t="s">
+        <v>10</v>
+      </c>
+      <c r="E6" t="s">
+        <v>7</v>
       </c>
       <c r="F6">
         <v>49.75</v>
@@ -507,18 +838,18 @@
         <v>199</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B7">
         <v>10</v>
       </c>
       <c r="C7">
         <v>32</v>
       </c>
-      <c r="D7" t="str">
-        <v>ترنج اولادى (انديجو)</v>
-      </c>
-      <c r="E7" t="str">
-        <v>بيبى ولد</v>
+      <c r="D7" t="s">
+        <v>9</v>
+      </c>
+      <c r="E7" t="s">
+        <v>7</v>
       </c>
       <c r="F7">
         <v>50</v>
@@ -527,18 +858,18 @@
         <v>200</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B8">
         <v>10</v>
       </c>
       <c r="C8">
         <v>33</v>
       </c>
-      <c r="D8" t="str">
-        <v>ترنج اولادى (منت)</v>
-      </c>
-      <c r="E8" t="str">
-        <v>بيبى ولد</v>
+      <c r="D8" t="s">
+        <v>6</v>
+      </c>
+      <c r="E8" t="s">
+        <v>7</v>
       </c>
       <c r="F8">
         <v>49.75</v>
@@ -547,18 +878,18 @@
         <v>199</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B9">
         <v>15</v>
       </c>
       <c r="C9">
         <v>58</v>
       </c>
-      <c r="D9" t="str">
-        <v>ترنج اولادى (منت)</v>
-      </c>
-      <c r="E9" t="str">
-        <v>بيبى ولد</v>
+      <c r="D9" t="s">
+        <v>6</v>
+      </c>
+      <c r="E9" t="s">
+        <v>7</v>
       </c>
       <c r="F9">
         <v>50</v>
@@ -567,18 +898,18 @@
         <v>200</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B10">
         <v>15</v>
       </c>
       <c r="C10">
         <v>59</v>
       </c>
-      <c r="D10" t="str">
-        <v>ترنج اولادى(رمادى)</v>
-      </c>
-      <c r="E10" t="str">
-        <v>بيبى ولد</v>
+      <c r="D10" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" t="s">
+        <v>7</v>
       </c>
       <c r="F10">
         <v>49.75</v>
@@ -587,18 +918,18 @@
         <v>199</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B11">
         <v>15</v>
       </c>
       <c r="C11">
         <v>60</v>
       </c>
-      <c r="D11" t="str">
-        <v>نرنج اولادى (انديجو)</v>
-      </c>
-      <c r="E11" t="str">
-        <v>بيبى ولد</v>
+      <c r="D11" t="s">
+        <v>12</v>
+      </c>
+      <c r="E11" t="s">
+        <v>7</v>
       </c>
       <c r="F11">
         <v>50</v>
@@ -607,18 +938,18 @@
         <v>200</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B12">
         <v>20</v>
       </c>
       <c r="C12">
         <v>61</v>
       </c>
-      <c r="D12" t="str">
-        <v>ترنج اولادى ( اسود)</v>
-      </c>
-      <c r="E12" t="str">
-        <v>بيبى ولد</v>
+      <c r="D12" t="s">
+        <v>13</v>
+      </c>
+      <c r="E12" t="s">
+        <v>7</v>
       </c>
       <c r="F12">
         <v>49.75</v>
@@ -627,18 +958,18 @@
         <v>199</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B13">
         <v>20</v>
       </c>
       <c r="C13">
         <v>62</v>
       </c>
-      <c r="D13" t="str">
-        <v>ترنج اولادى (كافيه)</v>
-      </c>
-      <c r="E13" t="str">
-        <v>بيبى ولد</v>
+      <c r="D13" t="s">
+        <v>14</v>
+      </c>
+      <c r="E13" t="s">
+        <v>7</v>
       </c>
       <c r="F13">
         <v>50</v>
@@ -647,18 +978,18 @@
         <v>200</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B14">
         <v>20</v>
       </c>
       <c r="C14">
         <v>63</v>
       </c>
-      <c r="D14" t="str">
-        <v>ترنج اولادى (انديجو)</v>
-      </c>
-      <c r="E14" t="str">
-        <v>بيبى ولد</v>
+      <c r="D14" t="s">
+        <v>9</v>
+      </c>
+      <c r="E14" t="s">
+        <v>7</v>
       </c>
       <c r="F14">
         <v>50</v>
@@ -667,18 +998,18 @@
         <v>200</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B15">
         <v>25</v>
       </c>
       <c r="C15">
         <v>106</v>
       </c>
-      <c r="D15" t="str">
-        <v>ترنج اولادى (شانيه)</v>
-      </c>
-      <c r="E15" t="str">
-        <v>بيبى ولد</v>
+      <c r="D15" t="s">
+        <v>15</v>
+      </c>
+      <c r="E15" t="s">
+        <v>7</v>
       </c>
       <c r="F15">
         <v>49</v>
@@ -687,18 +1018,18 @@
         <v>196</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B16">
         <v>25</v>
       </c>
       <c r="C16">
         <v>107</v>
       </c>
-      <c r="D16" t="str">
-        <v>ترنج اولادى( شاركول)</v>
-      </c>
-      <c r="E16" t="str">
-        <v>بيبى ولد</v>
+      <c r="D16" t="s">
+        <v>16</v>
+      </c>
+      <c r="E16" t="s">
+        <v>7</v>
       </c>
       <c r="F16">
         <v>50</v>
@@ -707,18 +1038,18 @@
         <v>200</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B17">
         <v>25</v>
       </c>
       <c r="C17">
         <v>108</v>
       </c>
-      <c r="D17" t="str">
-        <v>ترنج اولادى (كافيه)</v>
-      </c>
-      <c r="E17" t="str">
-        <v>بيبى ولد</v>
+      <c r="D17" t="s">
+        <v>14</v>
+      </c>
+      <c r="E17" t="s">
+        <v>7</v>
       </c>
       <c r="F17">
         <v>50</v>
@@ -727,18 +1058,18 @@
         <v>200</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B18">
         <v>30</v>
       </c>
       <c r="C18">
         <v>109</v>
       </c>
-      <c r="D18" t="str">
-        <v>ترنج اولادى(انديجو)</v>
-      </c>
-      <c r="E18" t="str">
-        <v>بيبى ولد</v>
+      <c r="D18" t="s">
+        <v>17</v>
+      </c>
+      <c r="E18" t="s">
+        <v>7</v>
       </c>
       <c r="F18">
         <v>48</v>
@@ -747,18 +1078,18 @@
         <v>192</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B19">
         <v>30</v>
       </c>
       <c r="C19">
         <v>110</v>
       </c>
-      <c r="D19" t="str">
-        <v>ترنج اولادى(تفاحى)</v>
-      </c>
-      <c r="E19" t="str">
-        <v>بيبى ولد</v>
+      <c r="D19" t="s">
+        <v>18</v>
+      </c>
+      <c r="E19" t="s">
+        <v>7</v>
       </c>
       <c r="F19">
         <v>49</v>
@@ -767,18 +1098,18 @@
         <v>196</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B20">
         <v>30</v>
       </c>
       <c r="C20">
         <v>111</v>
       </c>
-      <c r="D20" t="str">
-        <v>ترنج اولادى(بيج)</v>
-      </c>
-      <c r="E20" t="str">
-        <v>بيبى ولد</v>
+      <c r="D20" t="s">
+        <v>19</v>
+      </c>
+      <c r="E20" t="s">
+        <v>7</v>
       </c>
       <c r="F20">
         <v>50</v>
@@ -787,18 +1118,18 @@
         <v>200</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B21">
         <v>35</v>
       </c>
       <c r="C21">
         <v>94</v>
       </c>
-      <c r="D21" t="str">
-        <v>ترنج اولادى(تفاحى)</v>
-      </c>
-      <c r="E21" t="str">
-        <v>بيبى ولد</v>
+      <c r="D21" t="s">
+        <v>18</v>
+      </c>
+      <c r="E21" t="s">
+        <v>7</v>
       </c>
       <c r="F21">
         <v>49.75</v>
@@ -807,18 +1138,18 @@
         <v>199</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B22">
         <v>35</v>
       </c>
       <c r="C22">
         <v>95</v>
       </c>
-      <c r="D22" t="str">
-        <v>ترنج اولادى(اصفر)</v>
-      </c>
-      <c r="E22" t="str">
-        <v>بيبى ولد</v>
+      <c r="D22" t="s">
+        <v>20</v>
+      </c>
+      <c r="E22" t="s">
+        <v>7</v>
       </c>
       <c r="F22">
         <v>48</v>
@@ -827,18 +1158,18 @@
         <v>192</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B23">
         <v>35</v>
       </c>
       <c r="C23">
         <v>96</v>
       </c>
-      <c r="D23" t="str">
-        <v>ترنج اولادى(اورانج)</v>
-      </c>
-      <c r="E23" t="str">
-        <v>بيبى ولد</v>
+      <c r="D23" t="s">
+        <v>21</v>
+      </c>
+      <c r="E23" t="s">
+        <v>7</v>
       </c>
       <c r="F23">
         <v>50</v>
@@ -847,18 +1178,18 @@
         <v>200</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B24">
         <v>40</v>
       </c>
       <c r="C24">
         <v>97</v>
       </c>
-      <c r="D24" t="str">
-        <v>ترنج اولادى(اخضر)</v>
-      </c>
-      <c r="E24" t="str">
-        <v>بيبى ولد</v>
+      <c r="D24" t="s">
+        <v>22</v>
+      </c>
+      <c r="E24" t="s">
+        <v>7</v>
       </c>
       <c r="F24">
         <v>63</v>
@@ -867,18 +1198,18 @@
         <v>252</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B25">
         <v>40</v>
       </c>
       <c r="C25">
         <v>98</v>
       </c>
-      <c r="D25" t="str">
-        <v>ترنج اولادى (مسطرده)</v>
-      </c>
-      <c r="E25" t="str">
-        <v>بيبى ولد</v>
+      <c r="D25" t="s">
+        <v>23</v>
+      </c>
+      <c r="E25" t="s">
+        <v>7</v>
       </c>
       <c r="F25">
         <v>50</v>
@@ -887,18 +1218,18 @@
         <v>200</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B26">
         <v>40</v>
       </c>
       <c r="C26">
         <v>99</v>
       </c>
-      <c r="D26" t="str">
-        <v>ترنج اولادى ( احمر)</v>
-      </c>
-      <c r="E26" t="str">
-        <v>بيبى ولد</v>
+      <c r="D26" t="s">
+        <v>24</v>
+      </c>
+      <c r="E26" t="s">
+        <v>7</v>
       </c>
       <c r="F26">
         <v>50</v>
@@ -907,18 +1238,18 @@
         <v>200</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B27">
         <v>45</v>
       </c>
       <c r="C27">
         <v>148</v>
       </c>
-      <c r="D27" t="str">
-        <v>ترنج اولادى(اخضر)</v>
-      </c>
-      <c r="E27" t="str">
-        <v>بيبى ولد</v>
+      <c r="D27" t="s">
+        <v>22</v>
+      </c>
+      <c r="E27" t="s">
+        <v>7</v>
       </c>
       <c r="F27">
         <v>36</v>
@@ -927,18 +1258,18 @@
         <v>144</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B28">
         <v>45</v>
       </c>
       <c r="C28">
         <v>149</v>
       </c>
-      <c r="D28" t="str">
-        <v>ترنج اولادى(انديجو)</v>
-      </c>
-      <c r="E28" t="str">
-        <v>بيبى ولد</v>
+      <c r="D28" t="s">
+        <v>17</v>
+      </c>
+      <c r="E28" t="s">
+        <v>7</v>
       </c>
       <c r="F28">
         <v>14.75</v>
@@ -947,18 +1278,18 @@
         <v>59</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B29">
         <v>45</v>
       </c>
       <c r="C29">
         <v>150</v>
       </c>
-      <c r="D29" t="str">
-        <v>ترنج اولادى(هافان)</v>
-      </c>
-      <c r="E29" t="str">
-        <v>بيبى ولد</v>
+      <c r="D29" t="s">
+        <v>25</v>
+      </c>
+      <c r="E29" t="s">
+        <v>7</v>
       </c>
       <c r="F29">
         <v>50</v>
@@ -967,18 +1298,18 @@
         <v>200</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B30">
         <v>45</v>
       </c>
       <c r="C30">
         <v>151</v>
       </c>
-      <c r="D30" t="str">
-        <v>ترنج اولادى(كافيه)</v>
-      </c>
-      <c r="E30" t="str">
-        <v>بيبى ولد</v>
+      <c r="D30" t="s">
+        <v>26</v>
+      </c>
+      <c r="E30" t="s">
+        <v>7</v>
       </c>
       <c r="F30">
         <v>49</v>
@@ -987,18 +1318,18 @@
         <v>196</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B31">
         <v>50</v>
       </c>
       <c r="C31">
         <v>152</v>
       </c>
-      <c r="D31" t="str">
-        <v>ترنج اولادى(مسطرده)</v>
-      </c>
-      <c r="E31" t="str">
-        <v>بيبى ولد</v>
+      <c r="D31" t="s">
+        <v>27</v>
+      </c>
+      <c r="E31" t="s">
+        <v>7</v>
       </c>
       <c r="F31">
         <v>22</v>
@@ -1007,18 +1338,18 @@
         <v>88</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B32">
         <v>50</v>
       </c>
       <c r="C32">
         <v>153</v>
       </c>
-      <c r="D32" t="str">
-        <v>ترنج اولادى (تفاحى)</v>
-      </c>
-      <c r="E32" t="str">
-        <v>بيبى ولد</v>
+      <c r="D32" t="s">
+        <v>28</v>
+      </c>
+      <c r="E32" t="s">
+        <v>7</v>
       </c>
       <c r="F32">
         <v>27</v>
@@ -1027,18 +1358,18 @@
         <v>108</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B33">
         <v>50</v>
       </c>
       <c r="C33">
         <v>154</v>
       </c>
-      <c r="D33" t="str">
-        <v>ترنج اولادى (اورانج)</v>
-      </c>
-      <c r="E33" t="str">
-        <v>بيبى ولد</v>
+      <c r="D33" t="s">
+        <v>29</v>
+      </c>
+      <c r="E33" t="s">
+        <v>7</v>
       </c>
       <c r="F33">
         <v>49</v>
@@ -1047,18 +1378,18 @@
         <v>196</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B34">
         <v>50</v>
       </c>
       <c r="C34">
         <v>155</v>
       </c>
-      <c r="D34" t="str">
-        <v>ترنج اولادى(اصفر)</v>
-      </c>
-      <c r="E34" t="str">
-        <v>بيبى ولد</v>
+      <c r="D34" t="s">
+        <v>20</v>
+      </c>
+      <c r="E34" t="s">
+        <v>7</v>
       </c>
       <c r="F34">
         <v>48</v>
@@ -1067,18 +1398,18 @@
         <v>192</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B35">
         <v>55</v>
       </c>
       <c r="C35">
         <v>156</v>
       </c>
-      <c r="D35" t="str">
-        <v>ترنج اولادى (بيج)</v>
-      </c>
-      <c r="E35" t="str">
-        <v>بيبى ولد</v>
+      <c r="D35" t="s">
+        <v>30</v>
+      </c>
+      <c r="E35" t="s">
+        <v>7</v>
       </c>
       <c r="F35">
         <v>49.75</v>
@@ -1087,18 +1418,18 @@
         <v>199</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B36">
         <v>55</v>
       </c>
       <c r="C36">
         <v>157</v>
       </c>
-      <c r="D36" t="str">
-        <v>ترنج اولادى (بيطخى)</v>
-      </c>
-      <c r="E36" t="str">
-        <v>بيبى ولد</v>
+      <c r="D36" t="s">
+        <v>31</v>
+      </c>
+      <c r="E36" t="s">
+        <v>7</v>
       </c>
       <c r="F36">
         <v>50</v>
@@ -1107,18 +1438,18 @@
         <v>200</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B37">
         <v>55</v>
       </c>
       <c r="C37">
         <v>158</v>
       </c>
-      <c r="D37" t="str">
-        <v>ترنج اولادى(مسطرده)</v>
-      </c>
-      <c r="E37" t="str">
-        <v>بيبى ولد</v>
+      <c r="D37" t="s">
+        <v>27</v>
+      </c>
+      <c r="E37" t="s">
+        <v>7</v>
       </c>
       <c r="F37">
         <v>49</v>
@@ -1127,18 +1458,18 @@
         <v>196</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B38">
         <v>60</v>
       </c>
       <c r="C38">
         <v>188</v>
       </c>
-      <c r="D38" t="str">
-        <v>ترنج اولادى (زيتونى)</v>
-      </c>
-      <c r="E38" t="str">
-        <v>بيبى ولد</v>
+      <c r="D38" t="s">
+        <v>32</v>
+      </c>
+      <c r="E38" t="s">
+        <v>7</v>
       </c>
       <c r="F38">
         <v>50</v>
@@ -1147,18 +1478,18 @@
         <v>200</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B39">
         <v>60</v>
       </c>
       <c r="C39">
         <v>189</v>
       </c>
-      <c r="D39" t="str">
-        <v>ترنج اولادى(شاركول)</v>
-      </c>
-      <c r="E39" t="str">
-        <v>بيبى ولد</v>
+      <c r="D39" t="s">
+        <v>33</v>
+      </c>
+      <c r="E39" t="s">
+        <v>7</v>
       </c>
       <c r="F39">
         <v>50</v>
@@ -1167,18 +1498,18 @@
         <v>200</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B40">
         <v>60</v>
       </c>
       <c r="C40">
         <v>190</v>
       </c>
-      <c r="D40" t="str">
-        <v>ترنج اولادى (كافيه)</v>
-      </c>
-      <c r="E40" t="str">
-        <v>بيبى ولد</v>
+      <c r="D40" t="s">
+        <v>14</v>
+      </c>
+      <c r="E40" t="s">
+        <v>7</v>
       </c>
       <c r="F40">
         <v>47</v>
@@ -1187,18 +1518,18 @@
         <v>188</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B41">
         <v>65</v>
       </c>
       <c r="C41">
         <v>191</v>
       </c>
-      <c r="D41" t="str">
-        <v>ترنج اولادى( اسود)</v>
-      </c>
-      <c r="E41" t="str">
-        <v>بيبى ولد</v>
+      <c r="D41" t="s">
+        <v>34</v>
+      </c>
+      <c r="E41" t="s">
+        <v>7</v>
       </c>
       <c r="F41">
         <v>48</v>
@@ -1207,18 +1538,18 @@
         <v>192</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B42">
         <v>65</v>
       </c>
       <c r="C42">
         <v>192</v>
       </c>
-      <c r="D42" t="str">
-        <v>ترنج اولادى(زيتى)</v>
-      </c>
-      <c r="E42" t="str">
-        <v>بيبى ولد</v>
+      <c r="D42" t="s">
+        <v>35</v>
+      </c>
+      <c r="E42" t="s">
+        <v>7</v>
       </c>
       <c r="F42">
         <v>50</v>
@@ -1227,18 +1558,18 @@
         <v>200</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B43">
         <v>65</v>
       </c>
       <c r="C43">
         <v>193</v>
       </c>
-      <c r="D43" t="str">
-        <v>ترنج اولادى (منت)</v>
-      </c>
-      <c r="E43" t="str">
-        <v>بيبى ولد</v>
+      <c r="D43" t="s">
+        <v>6</v>
+      </c>
+      <c r="E43" t="s">
+        <v>7</v>
       </c>
       <c r="F43">
         <v>47</v>
@@ -1247,18 +1578,18 @@
         <v>188</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B44">
         <v>70</v>
       </c>
       <c r="C44">
         <v>236</v>
       </c>
-      <c r="D44" t="str">
-        <v>تر نج اولادى ( بستاج)</v>
-      </c>
-      <c r="E44" t="str">
-        <v>بيبى ولد</v>
+      <c r="D44" t="s">
+        <v>36</v>
+      </c>
+      <c r="E44" t="s">
+        <v>7</v>
       </c>
       <c r="F44">
         <v>19</v>
@@ -1267,18 +1598,18 @@
         <v>76</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B45">
         <v>70</v>
       </c>
       <c r="C45">
         <v>237</v>
       </c>
-      <c r="D45" t="str">
-        <v>ترنج اولادى(ابيض)</v>
-      </c>
-      <c r="E45" t="str">
-        <v>بيبى ولد</v>
+      <c r="D45" t="s">
+        <v>37</v>
+      </c>
+      <c r="E45" t="s">
+        <v>7</v>
       </c>
       <c r="F45">
         <v>26</v>
@@ -1287,18 +1618,18 @@
         <v>104</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B46">
         <v>70</v>
       </c>
       <c r="C46">
         <v>238</v>
       </c>
-      <c r="D46" t="str">
-        <v>ترنج اولادى ( كريمى)</v>
-      </c>
-      <c r="E46" t="str">
-        <v>بيبى ولد</v>
+      <c r="D46" t="s">
+        <v>38</v>
+      </c>
+      <c r="E46" t="s">
+        <v>7</v>
       </c>
       <c r="F46">
         <v>31</v>
@@ -1307,18 +1638,18 @@
         <v>124</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B47">
         <v>75</v>
       </c>
       <c r="C47">
         <v>233</v>
       </c>
-      <c r="D47" t="str">
-        <v>ترنج اولادى(منت)</v>
-      </c>
-      <c r="E47" t="str">
-        <v>بيبى ولد</v>
+      <c r="D47" t="s">
+        <v>39</v>
+      </c>
+      <c r="E47" t="s">
+        <v>7</v>
       </c>
       <c r="F47">
         <v>50</v>
@@ -1327,18 +1658,18 @@
         <v>200</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B48">
         <v>75</v>
       </c>
       <c r="C48">
         <v>234</v>
       </c>
-      <c r="D48" t="str">
-        <v>ترنج اولادى(انديجو)</v>
-      </c>
-      <c r="E48" t="str">
-        <v>بيبى ولد</v>
+      <c r="D48" t="s">
+        <v>17</v>
+      </c>
+      <c r="E48" t="s">
+        <v>7</v>
       </c>
       <c r="F48">
         <v>50</v>
@@ -1347,18 +1678,18 @@
         <v>200</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B49">
         <v>75</v>
       </c>
       <c r="C49">
         <v>235</v>
       </c>
-      <c r="D49" t="str">
-        <v>نرنج اولادى ( اورانج)</v>
-      </c>
-      <c r="E49" t="str">
-        <v>بيبى ولد</v>
+      <c r="D49" t="s">
+        <v>40</v>
+      </c>
+      <c r="E49" t="s">
+        <v>7</v>
       </c>
       <c r="F49">
         <v>44</v>
@@ -1367,18 +1698,18 @@
         <v>176</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B50">
         <v>80</v>
       </c>
       <c r="C50">
         <v>239</v>
       </c>
-      <c r="D50" t="str">
-        <v>ترنج اولادى (طوبى)</v>
-      </c>
-      <c r="E50" t="str">
-        <v>بيبى ولد</v>
+      <c r="D50" t="s">
+        <v>41</v>
+      </c>
+      <c r="E50" t="s">
+        <v>7</v>
       </c>
       <c r="F50">
         <v>30</v>
@@ -1387,18 +1718,18 @@
         <v>120</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B51">
         <v>80</v>
       </c>
       <c r="C51">
         <v>240</v>
       </c>
-      <c r="D51" t="str">
-        <v>ترنج اولادى (كشمير )</v>
-      </c>
-      <c r="E51" t="str">
-        <v>بيبى ولد</v>
+      <c r="D51" t="s">
+        <v>42</v>
+      </c>
+      <c r="E51" t="s">
+        <v>7</v>
       </c>
       <c r="F51">
         <v>38</v>
@@ -1407,18 +1738,18 @@
         <v>152</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B52">
         <v>80</v>
       </c>
       <c r="C52">
         <v>241</v>
       </c>
-      <c r="D52" t="str">
-        <v>ترنج اولادى( زيتونى)</v>
-      </c>
-      <c r="E52" t="str">
-        <v>بيبى ولد</v>
+      <c r="D52" t="s">
+        <v>43</v>
+      </c>
+      <c r="E52" t="s">
+        <v>7</v>
       </c>
       <c r="F52">
         <v>25</v>
@@ -1427,18 +1758,18 @@
         <v>100</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B53">
         <v>85</v>
       </c>
       <c r="C53">
         <v>242</v>
       </c>
-      <c r="D53" t="str">
-        <v>ترنج اولادى(اسود)</v>
-      </c>
-      <c r="E53" t="str">
-        <v>بيبى ولد</v>
+      <c r="D53" t="s">
+        <v>10</v>
+      </c>
+      <c r="E53" t="s">
+        <v>7</v>
       </c>
       <c r="F53">
         <v>24</v>
@@ -1447,18 +1778,18 @@
         <v>96</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B54">
         <v>85</v>
       </c>
       <c r="C54">
         <v>243</v>
       </c>
-      <c r="D54" t="str">
-        <v>ترنج اولادى(احمر)</v>
-      </c>
-      <c r="E54" t="str">
-        <v>بيبى ولد</v>
+      <c r="D54" t="s">
+        <v>44</v>
+      </c>
+      <c r="E54" t="s">
+        <v>7</v>
       </c>
       <c r="F54">
         <v>40</v>
@@ -1467,21 +1798,18 @@
         <v>160</v>
       </c>
     </row>
-    <row r="55">
-      <c r="A55">
-        <v>9404</v>
-      </c>
+    <row r="55" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B55">
         <v>85</v>
       </c>
       <c r="C55">
         <v>244</v>
       </c>
-      <c r="D55" t="str">
-        <v>ترنج اولادى(منت)</v>
-      </c>
-      <c r="E55" t="str">
-        <v>بيبى ولد</v>
+      <c r="D55" t="s">
+        <v>39</v>
+      </c>
+      <c r="E55" t="s">
+        <v>7</v>
       </c>
       <c r="F55">
         <v>33</v>
@@ -1490,18 +1818,18 @@
         <v>132</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B56">
         <v>100</v>
       </c>
       <c r="C56">
         <v>76</v>
       </c>
-      <c r="D56" t="str">
-        <v>ترنج اولادى (انديجو)</v>
-      </c>
-      <c r="E56" t="str">
-        <v>وسط ولد</v>
+      <c r="D56" t="s">
+        <v>9</v>
+      </c>
+      <c r="E56" t="s">
+        <v>45</v>
       </c>
       <c r="F56">
         <v>52</v>
@@ -1510,18 +1838,18 @@
         <v>208</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B57">
         <v>100</v>
       </c>
       <c r="C57">
         <v>78</v>
       </c>
-      <c r="D57" t="str">
-        <v>ترنج اولادى (بنى)</v>
-      </c>
-      <c r="E57" t="str">
-        <v>وسط ولد</v>
+      <c r="D57" t="s">
+        <v>46</v>
+      </c>
+      <c r="E57" t="s">
+        <v>45</v>
       </c>
       <c r="F57">
         <v>32</v>
@@ -1530,18 +1858,18 @@
         <v>128</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B58">
         <v>100</v>
       </c>
       <c r="C58">
         <v>77</v>
       </c>
-      <c r="D58" t="str">
-        <v>ترنج اولادى(اسود)</v>
-      </c>
-      <c r="E58" t="str">
-        <v>وسط ولد</v>
+      <c r="D58" t="s">
+        <v>10</v>
+      </c>
+      <c r="E58" t="s">
+        <v>45</v>
       </c>
       <c r="F58">
         <v>49.75</v>
@@ -1550,18 +1878,18 @@
         <v>199</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B59">
         <v>105</v>
       </c>
       <c r="C59">
         <v>79</v>
       </c>
-      <c r="D59" t="str">
-        <v>ترنج اولادى (شانيه)</v>
-      </c>
-      <c r="E59" t="str">
-        <v>وسط ولد</v>
+      <c r="D59" t="s">
+        <v>15</v>
+      </c>
+      <c r="E59" t="s">
+        <v>45</v>
       </c>
       <c r="F59">
         <v>59</v>
@@ -1570,18 +1898,18 @@
         <v>236</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B60">
         <v>105</v>
       </c>
       <c r="C60">
         <v>81</v>
       </c>
-      <c r="D60" t="str">
-        <v>ترنج اولادى(بطيخى)</v>
-      </c>
-      <c r="E60" t="str">
-        <v>وسط ولد</v>
+      <c r="D60" t="s">
+        <v>47</v>
+      </c>
+      <c r="E60" t="s">
+        <v>45</v>
       </c>
       <c r="F60">
         <v>60.75</v>
@@ -1590,18 +1918,18 @@
         <v>243</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B61">
         <v>105</v>
       </c>
       <c r="C61">
         <v>80</v>
       </c>
-      <c r="D61" t="str">
-        <v>ترنج اولادى (تفاحى)</v>
-      </c>
-      <c r="E61" t="str">
-        <v>وسط ولد</v>
+      <c r="D61" t="s">
+        <v>28</v>
+      </c>
+      <c r="E61" t="s">
+        <v>45</v>
       </c>
       <c r="F61">
         <v>59</v>
@@ -1610,18 +1938,18 @@
         <v>236</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B62">
         <v>110</v>
       </c>
       <c r="C62">
         <v>84</v>
       </c>
-      <c r="D62" t="str">
-        <v>ترنج اولادى(مسطرده)</v>
-      </c>
-      <c r="E62" t="str">
-        <v>وسط ولد</v>
+      <c r="D62" t="s">
+        <v>27</v>
+      </c>
+      <c r="E62" t="s">
+        <v>45</v>
       </c>
       <c r="F62">
         <v>50</v>
@@ -1630,18 +1958,18 @@
         <v>200</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B63">
         <v>110</v>
       </c>
       <c r="C63">
         <v>83</v>
       </c>
-      <c r="D63" t="str">
-        <v>ترنج اولادى(احمر)</v>
-      </c>
-      <c r="E63" t="str">
-        <v>وسط ولد</v>
+      <c r="D63" t="s">
+        <v>44</v>
+      </c>
+      <c r="E63" t="s">
+        <v>45</v>
       </c>
       <c r="F63">
         <v>50</v>
@@ -1650,18 +1978,18 @@
         <v>200</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B64">
         <v>110</v>
       </c>
       <c r="C64">
         <v>82</v>
       </c>
-      <c r="D64" t="str">
-        <v>ترنج اولادى(انديجو)</v>
-      </c>
-      <c r="E64" t="str">
-        <v>وسط ولد</v>
+      <c r="D64" t="s">
+        <v>17</v>
+      </c>
+      <c r="E64" t="s">
+        <v>45</v>
       </c>
       <c r="F64">
         <v>50</v>
@@ -1670,18 +1998,18 @@
         <v>200</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B65">
         <v>115</v>
       </c>
       <c r="C65">
         <v>159</v>
       </c>
-      <c r="D65" t="str">
-        <v>ترنج اولادى(اسود)</v>
-      </c>
-      <c r="E65" t="str">
-        <v>وسط ولد</v>
+      <c r="D65" t="s">
+        <v>10</v>
+      </c>
+      <c r="E65" t="s">
+        <v>45</v>
       </c>
       <c r="F65">
         <v>49</v>
@@ -1690,18 +2018,18 @@
         <v>196</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B66">
         <v>115</v>
       </c>
       <c r="C66">
         <v>161</v>
       </c>
-      <c r="D66" t="str">
-        <v>ترنج اولادى (رمادى)</v>
-      </c>
-      <c r="E66" t="str">
-        <v>وسط ولد</v>
+      <c r="D66" t="s">
+        <v>8</v>
+      </c>
+      <c r="E66" t="s">
+        <v>45</v>
       </c>
       <c r="F66">
         <v>49</v>
@@ -1710,18 +2038,18 @@
         <v>196</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B67">
         <v>115</v>
       </c>
       <c r="C67">
         <v>160</v>
       </c>
-      <c r="D67" t="str">
-        <v>ترنج اولادى(بيج)</v>
-      </c>
-      <c r="E67" t="str">
-        <v>وسط ولد</v>
+      <c r="D67" t="s">
+        <v>19</v>
+      </c>
+      <c r="E67" t="s">
+        <v>45</v>
       </c>
       <c r="F67">
         <v>50</v>
@@ -1730,18 +2058,18 @@
         <v>200</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B68">
         <v>120</v>
       </c>
       <c r="C68">
         <v>112</v>
       </c>
-      <c r="D68" t="str">
-        <v>ترنج اولادى(رمادى)</v>
-      </c>
-      <c r="E68" t="str">
-        <v>وسط ولد</v>
+      <c r="D68" t="s">
+        <v>11</v>
+      </c>
+      <c r="E68" t="s">
+        <v>45</v>
       </c>
       <c r="F68">
         <v>48</v>
@@ -1750,18 +2078,18 @@
         <v>192</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B69">
         <v>120</v>
       </c>
       <c r="C69">
         <v>113</v>
       </c>
-      <c r="D69" t="str">
-        <v>ترنج اولادى (شانيه)</v>
-      </c>
-      <c r="E69" t="str">
-        <v>وسط ولد</v>
+      <c r="D69" t="s">
+        <v>15</v>
+      </c>
+      <c r="E69" t="s">
+        <v>45</v>
       </c>
       <c r="F69">
         <v>49</v>
@@ -1770,18 +2098,18 @@
         <v>196</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B70">
         <v>120</v>
       </c>
       <c r="C70">
         <v>114</v>
       </c>
-      <c r="D70" t="str">
-        <v>ترنج اولادى (جيشى)</v>
-      </c>
-      <c r="E70" t="str">
-        <v>وسط ولد</v>
+      <c r="D70" t="s">
+        <v>48</v>
+      </c>
+      <c r="E70" t="s">
+        <v>45</v>
       </c>
       <c r="F70">
         <v>49</v>
@@ -1790,18 +2118,18 @@
         <v>196</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B71">
         <v>125</v>
       </c>
       <c r="C71">
         <v>103</v>
       </c>
-      <c r="D71" t="str">
-        <v>ترنج اولادى(اخضر)</v>
-      </c>
-      <c r="E71" t="str">
-        <v>وسط ولد</v>
+      <c r="D71" t="s">
+        <v>22</v>
+      </c>
+      <c r="E71" t="s">
+        <v>45</v>
       </c>
       <c r="F71">
         <v>50</v>
@@ -1810,18 +2138,18 @@
         <v>200</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B72">
         <v>125</v>
       </c>
       <c r="C72">
         <v>104</v>
       </c>
-      <c r="D72" t="str">
-        <v>ترنج اولادى(بطيخى)</v>
-      </c>
-      <c r="E72" t="str">
-        <v>وسط ولد</v>
+      <c r="D72" t="s">
+        <v>47</v>
+      </c>
+      <c r="E72" t="s">
+        <v>45</v>
       </c>
       <c r="F72">
         <v>50</v>
@@ -1830,18 +2158,18 @@
         <v>200</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B73">
         <v>125</v>
       </c>
       <c r="C73">
         <v>105</v>
       </c>
-      <c r="D73" t="str">
-        <v>ترنج اولادى(اصفر)</v>
-      </c>
-      <c r="E73" t="str">
-        <v>وسط ولد</v>
+      <c r="D73" t="s">
+        <v>20</v>
+      </c>
+      <c r="E73" t="s">
+        <v>45</v>
       </c>
       <c r="F73">
         <v>48</v>
@@ -1850,18 +2178,18 @@
         <v>192</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B74">
         <v>130</v>
       </c>
       <c r="C74">
         <v>143</v>
       </c>
-      <c r="D74" t="str">
-        <v>ترنج اولادى(مسطرده)</v>
-      </c>
-      <c r="E74" t="str">
-        <v>وسط ولد</v>
+      <c r="D74" t="s">
+        <v>27</v>
+      </c>
+      <c r="E74" t="s">
+        <v>45</v>
       </c>
       <c r="F74">
         <v>50</v>
@@ -1870,18 +2198,18 @@
         <v>200</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B75">
         <v>130</v>
       </c>
       <c r="C75">
         <v>144</v>
       </c>
-      <c r="D75" t="str">
-        <v>ترنج اولادى(بيج)</v>
-      </c>
-      <c r="E75" t="str">
-        <v>وسط ولد</v>
+      <c r="D75" t="s">
+        <v>19</v>
+      </c>
+      <c r="E75" t="s">
+        <v>45</v>
       </c>
       <c r="F75">
         <v>50</v>
@@ -1890,18 +2218,18 @@
         <v>200</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B76">
         <v>130</v>
       </c>
       <c r="C76">
         <v>142</v>
       </c>
-      <c r="D76" t="str">
-        <v>ترنج اولادى(اورانج)</v>
-      </c>
-      <c r="E76" t="str">
-        <v>وسط ولد</v>
+      <c r="D76" t="s">
+        <v>21</v>
+      </c>
+      <c r="E76" t="s">
+        <v>45</v>
       </c>
       <c r="F76">
         <v>50</v>
@@ -1910,18 +2238,18 @@
         <v>200</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B77">
         <v>135</v>
       </c>
       <c r="C77">
         <v>186</v>
       </c>
-      <c r="D77" t="str">
-        <v>ترنج اولادى(زيتونى)</v>
-      </c>
-      <c r="E77" t="str">
-        <v>وسط ولد</v>
+      <c r="D77" t="s">
+        <v>49</v>
+      </c>
+      <c r="E77" t="s">
+        <v>45</v>
       </c>
       <c r="F77">
         <v>49.5</v>
@@ -1930,18 +2258,18 @@
         <v>198</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B78">
         <v>135</v>
       </c>
       <c r="C78">
         <v>187</v>
       </c>
-      <c r="D78" t="str">
-        <v>ترنج اولادى(مسطرده)</v>
-      </c>
-      <c r="E78" t="str">
-        <v>وسط ولد</v>
+      <c r="D78" t="s">
+        <v>27</v>
+      </c>
+      <c r="E78" t="s">
+        <v>45</v>
       </c>
       <c r="F78">
         <v>50</v>
@@ -1950,18 +2278,18 @@
         <v>200</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B79">
         <v>135</v>
       </c>
       <c r="C79">
         <v>185</v>
       </c>
-      <c r="D79" t="str">
-        <v>ترنج اولادى (اورانج)</v>
-      </c>
-      <c r="E79" t="str">
-        <v>وسط ولد</v>
+      <c r="D79" t="s">
+        <v>29</v>
+      </c>
+      <c r="E79" t="s">
+        <v>45</v>
       </c>
       <c r="F79">
         <v>50</v>
@@ -1970,18 +2298,18 @@
         <v>200</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B80">
         <v>140</v>
       </c>
       <c r="C80">
         <v>197</v>
       </c>
-      <c r="D80" t="str">
-        <v>ترنج اولادى( اورانج)</v>
-      </c>
-      <c r="E80" t="str">
-        <v>وسط ولد</v>
+      <c r="D80" t="s">
+        <v>50</v>
+      </c>
+      <c r="E80" t="s">
+        <v>45</v>
       </c>
       <c r="F80">
         <v>49</v>
@@ -1990,18 +2318,18 @@
         <v>196</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B81">
         <v>140</v>
       </c>
       <c r="C81">
         <v>199</v>
       </c>
-      <c r="D81" t="str">
-        <v>ترنج اولادى(منت)</v>
-      </c>
-      <c r="E81" t="str">
-        <v>وسط ولد</v>
+      <c r="D81" t="s">
+        <v>39</v>
+      </c>
+      <c r="E81" t="s">
+        <v>45</v>
       </c>
       <c r="F81">
         <v>49</v>
@@ -2010,18 +2338,18 @@
         <v>196</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B82">
         <v>140</v>
       </c>
       <c r="C82">
         <v>198</v>
       </c>
-      <c r="D82" t="str">
-        <v>ترنج اولادى (بيج)</v>
-      </c>
-      <c r="E82" t="str">
-        <v>وسط ولد</v>
+      <c r="D82" t="s">
+        <v>30</v>
+      </c>
+      <c r="E82" t="s">
+        <v>45</v>
       </c>
       <c r="F82">
         <v>45</v>
@@ -2030,18 +2358,18 @@
         <v>180</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B83">
         <v>145</v>
       </c>
       <c r="C83">
         <v>196</v>
       </c>
-      <c r="D83" t="str">
-        <v>ترنج اولادى (جيشى)</v>
-      </c>
-      <c r="E83" t="str">
-        <v>وسط ولد</v>
+      <c r="D83" t="s">
+        <v>48</v>
+      </c>
+      <c r="E83" t="s">
+        <v>45</v>
       </c>
       <c r="F83">
         <v>49</v>
@@ -2050,18 +2378,18 @@
         <v>196</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B84">
         <v>145</v>
       </c>
       <c r="C84">
         <v>195</v>
       </c>
-      <c r="D84" t="str">
-        <v>ترنج اولادى(شانيه)</v>
-      </c>
-      <c r="E84" t="str">
-        <v>وسط ولد</v>
+      <c r="D84" t="s">
+        <v>51</v>
+      </c>
+      <c r="E84" t="s">
+        <v>45</v>
       </c>
       <c r="F84">
         <v>49</v>
@@ -2070,21 +2398,18 @@
         <v>196</v>
       </c>
     </row>
-    <row r="85">
-      <c r="A85">
-        <v>5976</v>
-      </c>
+    <row r="85" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B85">
         <v>145</v>
       </c>
       <c r="C85">
         <v>194</v>
       </c>
-      <c r="D85" t="str">
-        <v>ترنج اولادى(احمر)</v>
-      </c>
-      <c r="E85" t="str">
-        <v>وسط ولد</v>
+      <c r="D85" t="s">
+        <v>44</v>
+      </c>
+      <c r="E85" t="s">
+        <v>45</v>
       </c>
       <c r="F85">
         <v>49</v>
@@ -2093,18 +2418,18 @@
         <v>196</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B86">
         <v>300</v>
       </c>
       <c r="C86">
         <v>86</v>
       </c>
-      <c r="D86" t="str">
-        <v>ترنج اولادى (انديجو)</v>
-      </c>
-      <c r="E86" t="str">
-        <v>محير ولد</v>
+      <c r="D86" t="s">
+        <v>9</v>
+      </c>
+      <c r="E86" t="s">
+        <v>52</v>
       </c>
       <c r="F86">
         <v>48</v>
@@ -2113,18 +2438,18 @@
         <v>192</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B87">
         <v>300</v>
       </c>
       <c r="C87">
         <v>87</v>
       </c>
-      <c r="D87" t="str">
-        <v>ترنج اولادى(رمادى)</v>
-      </c>
-      <c r="E87" t="str">
-        <v>محير ولد</v>
+      <c r="D87" t="s">
+        <v>11</v>
+      </c>
+      <c r="E87" t="s">
+        <v>52</v>
       </c>
       <c r="F87">
         <v>49</v>
@@ -2133,18 +2458,18 @@
         <v>196</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B88">
         <v>300</v>
       </c>
       <c r="C88">
         <v>85</v>
       </c>
-      <c r="D88" t="str">
-        <v>ترنج اولادى( اسود)</v>
-      </c>
-      <c r="E88" t="str">
-        <v>محير ولد</v>
+      <c r="D88" t="s">
+        <v>34</v>
+      </c>
+      <c r="E88" t="s">
+        <v>52</v>
       </c>
       <c r="F88">
         <v>49</v>
@@ -2153,18 +2478,18 @@
         <v>196</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B89">
         <v>305</v>
       </c>
       <c r="C89">
         <v>89</v>
       </c>
-      <c r="D89" t="str">
-        <v>ترنج اولادى(مسطرده)</v>
-      </c>
-      <c r="E89" t="str">
-        <v>محير ولد</v>
+      <c r="D89" t="s">
+        <v>27</v>
+      </c>
+      <c r="E89" t="s">
+        <v>52</v>
       </c>
       <c r="F89">
         <v>60</v>
@@ -2173,18 +2498,18 @@
         <v>240</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B90">
         <v>305</v>
       </c>
       <c r="C90">
         <v>88</v>
       </c>
-      <c r="D90" t="str">
-        <v>ترنج اولادى(اخضر)</v>
-      </c>
-      <c r="E90" t="str">
-        <v>محبر ولد</v>
+      <c r="D90" t="s">
+        <v>22</v>
+      </c>
+      <c r="E90" t="s">
+        <v>53</v>
       </c>
       <c r="F90">
         <v>60</v>
@@ -2193,18 +2518,18 @@
         <v>240</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B91">
         <v>305</v>
       </c>
       <c r="C91">
         <v>90</v>
       </c>
-      <c r="D91" t="str">
-        <v>ترنج اولادى (هافان)</v>
-      </c>
-      <c r="E91" t="str">
-        <v>محير ولد</v>
+      <c r="D91" t="s">
+        <v>54</v>
+      </c>
+      <c r="E91" t="s">
+        <v>52</v>
       </c>
       <c r="F91">
         <v>60</v>
@@ -2213,18 +2538,18 @@
         <v>240</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B92">
         <v>310</v>
       </c>
       <c r="C92">
         <v>92</v>
       </c>
-      <c r="D92" t="str">
-        <v>ترنج اولادى (بيج)</v>
-      </c>
-      <c r="E92" t="str">
-        <v>محير ولد</v>
+      <c r="D92" t="s">
+        <v>30</v>
+      </c>
+      <c r="E92" t="s">
+        <v>52</v>
       </c>
       <c r="F92">
         <v>49</v>
@@ -2233,18 +2558,18 @@
         <v>196</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B93">
         <v>310</v>
       </c>
       <c r="C93">
         <v>93</v>
       </c>
-      <c r="D93" t="str">
-        <v>ترنج اولادى(جيشى)</v>
-      </c>
-      <c r="E93" t="str">
-        <v>محير ولد</v>
+      <c r="D93" t="s">
+        <v>55</v>
+      </c>
+      <c r="E93" t="s">
+        <v>52</v>
       </c>
       <c r="F93">
         <v>50</v>
@@ -2253,18 +2578,18 @@
         <v>200</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B94">
         <v>310</v>
       </c>
       <c r="C94">
         <v>91</v>
       </c>
-      <c r="D94" t="str">
-        <v>ترنج اولادى(احمر)</v>
-      </c>
-      <c r="E94" t="str">
-        <v>محير ولد</v>
+      <c r="D94" t="s">
+        <v>44</v>
+      </c>
+      <c r="E94" t="s">
+        <v>52</v>
       </c>
       <c r="F94">
         <v>49</v>
@@ -2273,18 +2598,18 @@
         <v>196</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B95">
         <v>315</v>
       </c>
       <c r="C95">
         <v>232</v>
       </c>
-      <c r="D95" t="str">
-        <v>ترنج اولادى(شانيه)</v>
-      </c>
-      <c r="E95" t="str">
-        <v>محير ولد</v>
+      <c r="D95" t="s">
+        <v>51</v>
+      </c>
+      <c r="E95" t="s">
+        <v>52</v>
       </c>
       <c r="F95">
         <v>41</v>
@@ -2293,18 +2618,18 @@
         <v>164</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B96">
         <v>315</v>
       </c>
       <c r="C96">
         <v>231</v>
       </c>
-      <c r="D96" t="str">
-        <v>ترنج اولادى(جيشى)</v>
-      </c>
-      <c r="E96" t="str">
-        <v>محير ولد</v>
+      <c r="D96" t="s">
+        <v>55</v>
+      </c>
+      <c r="E96" t="s">
+        <v>52</v>
       </c>
       <c r="F96">
         <v>49</v>
@@ -2313,18 +2638,18 @@
         <v>196</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B97">
         <v>315</v>
       </c>
       <c r="C97">
         <v>230</v>
       </c>
-      <c r="D97" t="str">
-        <v>ترنج اولادى(اسود)</v>
-      </c>
-      <c r="E97" t="str">
-        <v>محير ولد</v>
+      <c r="D97" t="s">
+        <v>10</v>
+      </c>
+      <c r="E97" t="s">
+        <v>52</v>
       </c>
       <c r="F97">
         <v>43</v>
@@ -2333,18 +2658,18 @@
         <v>172</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B98">
         <v>320</v>
       </c>
       <c r="C98">
         <v>117</v>
       </c>
-      <c r="D98" t="str">
-        <v>نرنج اولادى (كافيه)</v>
-      </c>
-      <c r="E98" t="str">
-        <v>محير ولد</v>
+      <c r="D98" t="s">
+        <v>56</v>
+      </c>
+      <c r="E98" t="s">
+        <v>52</v>
       </c>
       <c r="F98">
         <v>50</v>
@@ -2353,18 +2678,18 @@
         <v>200</v>
       </c>
     </row>
-    <row r="99">
+    <row r="99" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B99">
         <v>320</v>
       </c>
       <c r="C99">
         <v>116</v>
       </c>
-      <c r="D99" t="str">
-        <v>ترنج اولادى (شاركول)</v>
-      </c>
-      <c r="E99" t="str">
-        <v>محير ولد</v>
+      <c r="D99" t="s">
+        <v>57</v>
+      </c>
+      <c r="E99" t="s">
+        <v>52</v>
       </c>
       <c r="F99">
         <v>49</v>
@@ -2373,18 +2698,18 @@
         <v>196</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B100">
         <v>320</v>
       </c>
       <c r="C100">
         <v>115</v>
       </c>
-      <c r="D100" t="str">
-        <v>ترنج اولادى (اسود)</v>
-      </c>
-      <c r="E100" t="str">
-        <v>محير ولد</v>
+      <c r="D100" t="s">
+        <v>58</v>
+      </c>
+      <c r="E100" t="s">
+        <v>52</v>
       </c>
       <c r="F100">
         <v>50</v>
@@ -2393,18 +2718,18 @@
         <v>200</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B101">
         <v>325</v>
       </c>
       <c r="C101">
         <v>100</v>
       </c>
-      <c r="D101" t="str">
-        <v>ترنج اولادى(احمر)</v>
-      </c>
-      <c r="E101" t="str">
-        <v>محبر ولد</v>
+      <c r="D101" t="s">
+        <v>44</v>
+      </c>
+      <c r="E101" t="s">
+        <v>53</v>
       </c>
       <c r="F101">
         <v>50</v>
@@ -2413,18 +2738,18 @@
         <v>200</v>
       </c>
     </row>
-    <row r="102">
+    <row r="102" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B102">
         <v>325</v>
       </c>
       <c r="C102">
         <v>101</v>
       </c>
-      <c r="D102" t="str">
-        <v>ترنج اولادى(انديجو)</v>
-      </c>
-      <c r="E102" t="str">
-        <v>محير ولد</v>
+      <c r="D102" t="s">
+        <v>17</v>
+      </c>
+      <c r="E102" t="s">
+        <v>52</v>
       </c>
       <c r="F102">
         <v>50</v>
@@ -2433,18 +2758,18 @@
         <v>200</v>
       </c>
     </row>
-    <row r="103">
+    <row r="103" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B103">
         <v>325</v>
       </c>
       <c r="C103">
         <v>102</v>
       </c>
-      <c r="D103" t="str">
-        <v>ترنج اولادى (مسطرده)</v>
-      </c>
-      <c r="E103" t="str">
-        <v>محير ولد</v>
+      <c r="D103" t="s">
+        <v>23</v>
+      </c>
+      <c r="E103" t="s">
+        <v>52</v>
       </c>
       <c r="F103">
         <v>50</v>
@@ -2453,18 +2778,18 @@
         <v>200</v>
       </c>
     </row>
-    <row r="104">
+    <row r="104" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B104">
         <v>330</v>
       </c>
       <c r="C104">
         <v>145</v>
       </c>
-      <c r="D104" t="str">
-        <v>ترنج اولادى(ابيض)</v>
-      </c>
-      <c r="E104" t="str">
-        <v>محير ولد</v>
+      <c r="D104" t="s">
+        <v>37</v>
+      </c>
+      <c r="E104" t="s">
+        <v>52</v>
       </c>
       <c r="F104">
         <v>48</v>
@@ -2473,18 +2798,18 @@
         <v>192</v>
       </c>
     </row>
-    <row r="105">
+    <row r="105" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B105">
         <v>330</v>
       </c>
       <c r="C105">
         <v>147</v>
       </c>
-      <c r="D105" t="str">
-        <v>ترنج اولادى(منت)</v>
-      </c>
-      <c r="E105" t="str">
-        <v>محير ولد</v>
+      <c r="D105" t="s">
+        <v>39</v>
+      </c>
+      <c r="E105" t="s">
+        <v>52</v>
       </c>
       <c r="F105">
         <v>39</v>
@@ -2493,18 +2818,18 @@
         <v>156</v>
       </c>
     </row>
-    <row r="106">
+    <row r="106" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B106">
         <v>330</v>
       </c>
       <c r="C106">
         <v>146</v>
       </c>
-      <c r="D106" t="str">
-        <v>ترنج اولادى (تفاحى)</v>
-      </c>
-      <c r="E106" t="str">
-        <v>محير ولد</v>
+      <c r="D106" t="s">
+        <v>28</v>
+      </c>
+      <c r="E106" t="s">
+        <v>52</v>
       </c>
       <c r="F106">
         <v>47</v>
@@ -2513,18 +2838,18 @@
         <v>188</v>
       </c>
     </row>
-    <row r="107">
+    <row r="107" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B107">
         <v>335</v>
       </c>
       <c r="C107">
         <v>182</v>
       </c>
-      <c r="D107" t="str">
-        <v>ترنج اولادى (احمر)</v>
-      </c>
-      <c r="E107" t="str">
-        <v>محير ولد</v>
+      <c r="D107" t="s">
+        <v>59</v>
+      </c>
+      <c r="E107" t="s">
+        <v>52</v>
       </c>
       <c r="F107">
         <v>49</v>
@@ -2533,18 +2858,18 @@
         <v>196</v>
       </c>
     </row>
-    <row r="108">
+    <row r="108" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B108">
         <v>335</v>
       </c>
       <c r="C108">
         <v>183</v>
       </c>
-      <c r="D108" t="str">
-        <v>ترنج اولادى(بيج)</v>
-      </c>
-      <c r="E108" t="str">
-        <v>محير ولد</v>
+      <c r="D108" t="s">
+        <v>19</v>
+      </c>
+      <c r="E108" t="s">
+        <v>52</v>
       </c>
       <c r="F108">
         <v>49.5</v>
@@ -2553,18 +2878,18 @@
         <v>198</v>
       </c>
     </row>
-    <row r="109">
+    <row r="109" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B109">
         <v>335</v>
       </c>
       <c r="C109">
         <v>184</v>
       </c>
-      <c r="D109" t="str">
-        <v>ترنج اولادى( هافان)</v>
-      </c>
-      <c r="E109" t="str">
-        <v>محير ولد</v>
+      <c r="D109" t="s">
+        <v>60</v>
+      </c>
+      <c r="E109" t="s">
+        <v>52</v>
       </c>
       <c r="F109">
         <v>48</v>
@@ -2573,18 +2898,18 @@
         <v>192</v>
       </c>
     </row>
-    <row r="110">
+    <row r="110" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B110">
         <v>340</v>
       </c>
       <c r="C110">
         <v>204</v>
       </c>
-      <c r="D110" t="str">
-        <v>ترنج اولادى (شانيه)</v>
-      </c>
-      <c r="E110" t="str">
-        <v>محير ولد</v>
+      <c r="D110" t="s">
+        <v>15</v>
+      </c>
+      <c r="E110" t="s">
+        <v>52</v>
       </c>
       <c r="F110">
         <v>46</v>
@@ -2593,18 +2918,18 @@
         <v>184</v>
       </c>
     </row>
-    <row r="111">
+    <row r="111" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B111">
         <v>340</v>
       </c>
       <c r="C111">
         <v>203</v>
       </c>
-      <c r="D111" t="str">
-        <v>ترنج اولادى ( اسود)</v>
-      </c>
-      <c r="E111" t="str">
-        <v>محير ولد</v>
+      <c r="D111" t="s">
+        <v>13</v>
+      </c>
+      <c r="E111" t="s">
+        <v>52</v>
       </c>
       <c r="F111">
         <v>45</v>
@@ -2613,18 +2938,18 @@
         <v>180</v>
       </c>
     </row>
-    <row r="112">
+    <row r="112" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B112">
         <v>345</v>
       </c>
       <c r="C112">
         <v>207</v>
       </c>
-      <c r="D112" t="str">
-        <v>ترنج اولادى (منت)</v>
-      </c>
-      <c r="E112" t="str">
-        <v>محير ولد</v>
+      <c r="D112" t="s">
+        <v>6</v>
+      </c>
+      <c r="E112" t="s">
+        <v>52</v>
       </c>
       <c r="F112">
         <v>48</v>
@@ -2633,18 +2958,18 @@
         <v>192</v>
       </c>
     </row>
-    <row r="113">
+    <row r="113" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B113">
         <v>345</v>
       </c>
       <c r="C113">
         <v>208</v>
       </c>
-      <c r="D113" t="str">
-        <v>ترنج اولادى(هافان)</v>
-      </c>
-      <c r="E113" t="str">
-        <v>محير ولد</v>
+      <c r="D113" t="s">
+        <v>25</v>
+      </c>
+      <c r="E113" t="s">
+        <v>52</v>
       </c>
       <c r="F113">
         <v>39</v>
@@ -2653,21 +2978,18 @@
         <v>156</v>
       </c>
     </row>
-    <row r="114">
-      <c r="A114">
-        <v>5606</v>
-      </c>
+    <row r="114" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B114">
         <v>345</v>
       </c>
       <c r="C114">
         <v>206</v>
       </c>
-      <c r="D114" t="str">
-        <v>ترنج اولادى(اسود)</v>
-      </c>
-      <c r="E114" t="str">
-        <v>محير ولد</v>
+      <c r="D114" t="s">
+        <v>10</v>
+      </c>
+      <c r="E114" t="s">
+        <v>52</v>
       </c>
       <c r="F114">
         <v>37</v>
@@ -2676,18 +2998,18 @@
         <v>148</v>
       </c>
     </row>
-    <row r="115">
+    <row r="115" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B115">
         <v>500</v>
       </c>
       <c r="C115">
         <v>64</v>
       </c>
-      <c r="D115" t="str">
-        <v>ترنج بناتى (انديجو)</v>
-      </c>
-      <c r="E115" t="str">
-        <v>بيبى بنت</v>
+      <c r="D115" t="s">
+        <v>61</v>
+      </c>
+      <c r="E115" t="s">
+        <v>62</v>
       </c>
       <c r="F115">
         <v>50</v>
@@ -2696,18 +3018,18 @@
         <v>200</v>
       </c>
     </row>
-    <row r="116">
+    <row r="116" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B116">
         <v>500</v>
       </c>
       <c r="C116">
         <v>65</v>
       </c>
-      <c r="D116" t="str">
-        <v>ترنج بناتى(موف)</v>
-      </c>
-      <c r="E116" t="str">
-        <v>بيبى بنت</v>
+      <c r="D116" t="s">
+        <v>63</v>
+      </c>
+      <c r="E116" t="s">
+        <v>62</v>
       </c>
       <c r="F116">
         <v>58</v>
@@ -2716,18 +3038,18 @@
         <v>232</v>
       </c>
     </row>
-    <row r="117">
+    <row r="117" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B117">
         <v>500</v>
       </c>
       <c r="C117">
         <v>66</v>
       </c>
-      <c r="D117" t="str">
-        <v>ترنج بناتى ( رمادى)</v>
-      </c>
-      <c r="E117" t="str">
-        <v>بيبى بنت</v>
+      <c r="D117" t="s">
+        <v>64</v>
+      </c>
+      <c r="E117" t="s">
+        <v>62</v>
       </c>
       <c r="F117">
         <v>50</v>
@@ -2736,18 +3058,18 @@
         <v>200</v>
       </c>
     </row>
-    <row r="118">
+    <row r="118" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B118">
         <v>505</v>
       </c>
       <c r="C118">
         <v>67</v>
       </c>
-      <c r="D118" t="str">
-        <v>ترنج بناتى(كافيه)</v>
-      </c>
-      <c r="E118" t="str">
-        <v>بيبي بنت</v>
+      <c r="D118" t="s">
+        <v>65</v>
+      </c>
+      <c r="E118" t="s">
+        <v>66</v>
       </c>
       <c r="F118">
         <v>50</v>
@@ -2756,18 +3078,18 @@
         <v>200</v>
       </c>
     </row>
-    <row r="119">
+    <row r="119" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B119">
         <v>505</v>
       </c>
       <c r="C119">
         <v>69</v>
       </c>
-      <c r="D119" t="str">
-        <v>ترنج بناتى (ابيض)</v>
-      </c>
-      <c r="E119" t="str">
-        <v>بيبى بنت</v>
+      <c r="D119" t="s">
+        <v>67</v>
+      </c>
+      <c r="E119" t="s">
+        <v>62</v>
       </c>
       <c r="F119">
         <v>49</v>
@@ -2776,18 +3098,18 @@
         <v>196</v>
       </c>
     </row>
-    <row r="120">
+    <row r="120" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B120">
         <v>505</v>
       </c>
       <c r="C120">
         <v>68</v>
       </c>
-      <c r="D120" t="str">
-        <v>ترنج بناتى (منت)</v>
-      </c>
-      <c r="E120" t="str">
-        <v>بيبى بنت</v>
+      <c r="D120" t="s">
+        <v>68</v>
+      </c>
+      <c r="E120" t="s">
+        <v>62</v>
       </c>
       <c r="F120">
         <v>49.5</v>
@@ -2796,18 +3118,18 @@
         <v>198</v>
       </c>
     </row>
-    <row r="121">
+    <row r="121" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B121">
         <v>510</v>
       </c>
       <c r="C121">
         <v>71</v>
       </c>
-      <c r="D121" t="str">
-        <v>ترنج بناتى (برجاندى)</v>
-      </c>
-      <c r="E121" t="str">
-        <v>بيبى بنت</v>
+      <c r="D121" t="s">
+        <v>69</v>
+      </c>
+      <c r="E121" t="s">
+        <v>62</v>
       </c>
       <c r="F121">
         <v>49.75</v>
@@ -2816,18 +3138,18 @@
         <v>199</v>
       </c>
     </row>
-    <row r="122">
+    <row r="122" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B122">
         <v>510</v>
       </c>
       <c r="C122">
         <v>70</v>
       </c>
-      <c r="D122" t="str">
-        <v>ترنج بناتى (انديجو)</v>
-      </c>
-      <c r="E122" t="str">
-        <v>بيبى بنت</v>
+      <c r="D122" t="s">
+        <v>61</v>
+      </c>
+      <c r="E122" t="s">
+        <v>62</v>
       </c>
       <c r="F122">
         <v>49.75</v>
@@ -2836,18 +3158,18 @@
         <v>199</v>
       </c>
     </row>
-    <row r="123">
+    <row r="123" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B123">
         <v>510</v>
       </c>
       <c r="C123">
         <v>72</v>
       </c>
-      <c r="D123" t="str">
-        <v>ترنج بناتى (اوف ويت)</v>
-      </c>
-      <c r="E123" t="str">
-        <v>بيبى بنت</v>
+      <c r="D123" t="s">
+        <v>70</v>
+      </c>
+      <c r="E123" t="s">
+        <v>62</v>
       </c>
       <c r="F123">
         <v>47</v>
@@ -2856,18 +3178,18 @@
         <v>188</v>
       </c>
     </row>
-    <row r="124">
+    <row r="124" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B124">
         <v>515</v>
       </c>
       <c r="C124">
         <v>73</v>
       </c>
-      <c r="D124" t="str">
-        <v>ترنج بناتى(ابيض)</v>
-      </c>
-      <c r="E124" t="str">
-        <v>بيبى بنت</v>
+      <c r="D124" t="s">
+        <v>71</v>
+      </c>
+      <c r="E124" t="s">
+        <v>62</v>
       </c>
       <c r="F124">
         <v>50</v>
@@ -2876,18 +3198,18 @@
         <v>200</v>
       </c>
     </row>
-    <row r="125">
+    <row r="125" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B125">
         <v>515</v>
       </c>
       <c r="C125">
         <v>75</v>
       </c>
-      <c r="D125" t="str">
-        <v>ترنج بناتى(رمادى)</v>
-      </c>
-      <c r="E125" t="str">
-        <v>بيبى بنت</v>
+      <c r="D125" t="s">
+        <v>72</v>
+      </c>
+      <c r="E125" t="s">
+        <v>62</v>
       </c>
       <c r="F125">
         <v>50</v>
@@ -2896,18 +3218,18 @@
         <v>200</v>
       </c>
     </row>
-    <row r="126">
+    <row r="126" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B126">
         <v>515</v>
       </c>
       <c r="C126">
         <v>74</v>
       </c>
-      <c r="D126" t="str">
-        <v>ترنج بناتى (لبنى)</v>
-      </c>
-      <c r="E126" t="str">
-        <v>بيبى بنت</v>
+      <c r="D126" t="s">
+        <v>73</v>
+      </c>
+      <c r="E126" t="s">
+        <v>62</v>
       </c>
       <c r="F126">
         <v>50.75</v>
@@ -2916,18 +3238,18 @@
         <v>203</v>
       </c>
     </row>
-    <row r="127">
+    <row r="127" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B127">
         <v>520</v>
       </c>
       <c r="C127">
         <v>176</v>
       </c>
-      <c r="D127" t="str">
-        <v>ترنج بناتى(فوشيا)</v>
-      </c>
-      <c r="E127" t="str">
-        <v>بيبى بنت</v>
+      <c r="D127" t="s">
+        <v>74</v>
+      </c>
+      <c r="E127" t="s">
+        <v>62</v>
       </c>
       <c r="F127">
         <v>50</v>
@@ -2936,18 +3258,18 @@
         <v>200</v>
       </c>
     </row>
-    <row r="128">
+    <row r="128" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B128">
         <v>520</v>
       </c>
       <c r="C128">
         <v>175</v>
       </c>
-      <c r="D128" t="str">
-        <v>ترنج بناتى(بستاج)</v>
-      </c>
-      <c r="E128" t="str">
-        <v>بيبى بنت</v>
+      <c r="D128" t="s">
+        <v>75</v>
+      </c>
+      <c r="E128" t="s">
+        <v>62</v>
       </c>
       <c r="F128">
         <v>50</v>
@@ -2956,18 +3278,18 @@
         <v>200</v>
       </c>
     </row>
-    <row r="129">
+    <row r="129" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B129">
         <v>520</v>
       </c>
       <c r="C129">
         <v>177</v>
       </c>
-      <c r="D129" t="str">
-        <v>ترنج بناتى(موف)</v>
-      </c>
-      <c r="E129" t="str">
-        <v>بيبى بنت</v>
+      <c r="D129" t="s">
+        <v>63</v>
+      </c>
+      <c r="E129" t="s">
+        <v>62</v>
       </c>
       <c r="F129">
         <v>49</v>
@@ -2976,18 +3298,18 @@
         <v>196</v>
       </c>
     </row>
-    <row r="130">
+    <row r="130" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B130">
         <v>525</v>
       </c>
       <c r="C130">
         <v>173</v>
       </c>
-      <c r="D130" t="str">
-        <v>ترنج بناتى (سميون)</v>
-      </c>
-      <c r="E130" t="str">
-        <v>بيبى بنت</v>
+      <c r="D130" t="s">
+        <v>76</v>
+      </c>
+      <c r="E130" t="s">
+        <v>62</v>
       </c>
       <c r="F130">
         <v>50</v>
@@ -2996,18 +3318,18 @@
         <v>200</v>
       </c>
     </row>
-    <row r="131">
+    <row r="131" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B131">
         <v>525</v>
       </c>
       <c r="C131">
         <v>172</v>
       </c>
-      <c r="D131" t="str">
-        <v>ترنج بناتى (اصفر)</v>
-      </c>
-      <c r="E131" t="str">
-        <v>بيبى بنت</v>
+      <c r="D131" t="s">
+        <v>77</v>
+      </c>
+      <c r="E131" t="s">
+        <v>62</v>
       </c>
       <c r="F131">
         <v>49</v>
@@ -3016,18 +3338,18 @@
         <v>196</v>
       </c>
     </row>
-    <row r="132">
+    <row r="132" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B132">
         <v>525</v>
       </c>
       <c r="C132">
         <v>174</v>
       </c>
-      <c r="D132" t="str">
-        <v>ترنج بناتى (روز)</v>
-      </c>
-      <c r="E132" t="str">
-        <v>بيبى بنت</v>
+      <c r="D132" t="s">
+        <v>78</v>
+      </c>
+      <c r="E132" t="s">
+        <v>62</v>
       </c>
       <c r="F132">
         <v>49</v>
@@ -3036,18 +3358,18 @@
         <v>196</v>
       </c>
     </row>
-    <row r="133">
+    <row r="133" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B133">
         <v>530</v>
       </c>
       <c r="C133">
         <v>162</v>
       </c>
-      <c r="D133" t="str">
-        <v>ترنج بناتى( تفاحى)</v>
-      </c>
-      <c r="E133" t="str">
-        <v>بيبى بنت</v>
+      <c r="D133" t="s">
+        <v>79</v>
+      </c>
+      <c r="E133" t="s">
+        <v>62</v>
       </c>
       <c r="F133">
         <v>49.75</v>
@@ -3056,18 +3378,18 @@
         <v>199</v>
       </c>
     </row>
-    <row r="134">
+    <row r="134" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B134">
         <v>530</v>
       </c>
       <c r="C134">
         <v>164</v>
       </c>
-      <c r="D134" t="str">
-        <v>ترنج بناتى(سميون)</v>
-      </c>
-      <c r="E134" t="str">
-        <v>بيبى بنت</v>
+      <c r="D134" t="s">
+        <v>80</v>
+      </c>
+      <c r="E134" t="s">
+        <v>62</v>
       </c>
       <c r="F134">
         <v>50</v>
@@ -3076,18 +3398,18 @@
         <v>200</v>
       </c>
     </row>
-    <row r="135">
+    <row r="135" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B135">
         <v>530</v>
       </c>
       <c r="C135">
         <v>163</v>
       </c>
-      <c r="D135" t="str">
-        <v>ترنج بناتى(موف)</v>
-      </c>
-      <c r="E135" t="str">
-        <v>بيبى بنت</v>
+      <c r="D135" t="s">
+        <v>63</v>
+      </c>
+      <c r="E135" t="s">
+        <v>62</v>
       </c>
       <c r="F135">
         <v>49.5</v>
@@ -3096,18 +3418,18 @@
         <v>198</v>
       </c>
     </row>
-    <row r="136">
+    <row r="136" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B136">
         <v>535</v>
       </c>
       <c r="C136">
         <v>178</v>
       </c>
-      <c r="D136" t="str">
-        <v>ترنج بناتى(اصفر)</v>
-      </c>
-      <c r="E136" t="str">
-        <v>بيبى بنت</v>
+      <c r="D136" t="s">
+        <v>81</v>
+      </c>
+      <c r="E136" t="s">
+        <v>62</v>
       </c>
       <c r="F136">
         <v>48</v>
@@ -3116,18 +3438,18 @@
         <v>192</v>
       </c>
     </row>
-    <row r="137">
+    <row r="137" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B137">
         <v>535</v>
       </c>
       <c r="C137">
         <v>179</v>
       </c>
-      <c r="D137" t="str">
-        <v>ترنج بناتى(سميون)</v>
-      </c>
-      <c r="E137" t="str">
-        <v>بيبى بنت</v>
+      <c r="D137" t="s">
+        <v>80</v>
+      </c>
+      <c r="E137" t="s">
+        <v>62</v>
       </c>
       <c r="F137">
         <v>50</v>
@@ -3136,18 +3458,18 @@
         <v>200</v>
       </c>
     </row>
-    <row r="138">
+    <row r="138" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B138">
         <v>535</v>
       </c>
       <c r="C138">
         <v>180</v>
       </c>
-      <c r="D138" t="str">
-        <v>ترنج بناتى(روز)</v>
-      </c>
-      <c r="E138" t="str">
-        <v>بيبى بنت</v>
+      <c r="D138" t="s">
+        <v>82</v>
+      </c>
+      <c r="E138" t="s">
+        <v>62</v>
       </c>
       <c r="F138">
         <v>33</v>
@@ -3156,18 +3478,18 @@
         <v>132</v>
       </c>
     </row>
-    <row r="139">
+    <row r="139" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B139">
         <v>535</v>
       </c>
       <c r="C139">
         <v>181</v>
       </c>
-      <c r="D139" t="str">
-        <v>ترنج بناتى (موف)</v>
-      </c>
-      <c r="E139" t="str">
-        <v>بيبى بنت</v>
+      <c r="D139" t="s">
+        <v>83</v>
+      </c>
+      <c r="E139" t="s">
+        <v>62</v>
       </c>
       <c r="F139">
         <v>15</v>
@@ -3176,18 +3498,18 @@
         <v>60</v>
       </c>
     </row>
-    <row r="140">
+    <row r="140" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B140">
         <v>540</v>
       </c>
       <c r="C140">
         <v>214</v>
       </c>
-      <c r="D140" t="str">
-        <v>ترنج بناتى(فوشيا)</v>
-      </c>
-      <c r="E140" t="str">
-        <v>بيبى بنت</v>
+      <c r="D140" t="s">
+        <v>74</v>
+      </c>
+      <c r="E140" t="s">
+        <v>62</v>
       </c>
       <c r="F140">
         <v>47</v>
@@ -3196,18 +3518,18 @@
         <v>188</v>
       </c>
     </row>
-    <row r="141">
+    <row r="141" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B141">
         <v>540</v>
       </c>
       <c r="C141">
         <v>213</v>
       </c>
-      <c r="D141" t="str">
-        <v>ترنج بناتى(بيج)</v>
-      </c>
-      <c r="E141" t="str">
-        <v>بيبى بنت</v>
+      <c r="D141" t="s">
+        <v>84</v>
+      </c>
+      <c r="E141" t="s">
+        <v>62</v>
       </c>
       <c r="F141">
         <v>47</v>
@@ -3216,18 +3538,18 @@
         <v>188</v>
       </c>
     </row>
-    <row r="142">
+    <row r="142" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B142">
         <v>540</v>
       </c>
       <c r="C142">
         <v>212</v>
       </c>
-      <c r="D142" t="str">
-        <v>ترنج بناتى(اصفر)</v>
-      </c>
-      <c r="E142" t="str">
-        <v>بيبى بنت</v>
+      <c r="D142" t="s">
+        <v>81</v>
+      </c>
+      <c r="E142" t="s">
+        <v>62</v>
       </c>
       <c r="F142">
         <v>49</v>
@@ -3236,18 +3558,18 @@
         <v>196</v>
       </c>
     </row>
-    <row r="143">
+    <row r="143" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B143">
         <v>545</v>
       </c>
       <c r="C143">
         <v>217</v>
       </c>
-      <c r="D143" t="str">
-        <v>ترنج بناتى ( تفاحى)</v>
-      </c>
-      <c r="E143" t="str">
-        <v>بيبى بنت</v>
+      <c r="D143" t="s">
+        <v>85</v>
+      </c>
+      <c r="E143" t="s">
+        <v>62</v>
       </c>
       <c r="F143">
         <v>38</v>
@@ -3256,18 +3578,18 @@
         <v>152</v>
       </c>
     </row>
-    <row r="144">
+    <row r="144" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B144">
         <v>545</v>
       </c>
       <c r="C144">
         <v>216</v>
       </c>
-      <c r="D144" t="str">
-        <v>ترنج بناتى ( بدى روز)</v>
-      </c>
-      <c r="E144" t="str">
-        <v>بيبى بنت</v>
+      <c r="D144" t="s">
+        <v>86</v>
+      </c>
+      <c r="E144" t="s">
+        <v>62</v>
       </c>
       <c r="F144">
         <v>45</v>
@@ -3276,21 +3598,18 @@
         <v>180</v>
       </c>
     </row>
-    <row r="145">
-      <c r="A145">
-        <v>5884</v>
-      </c>
+    <row r="145" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B145">
         <v>545</v>
       </c>
       <c r="C145">
         <v>215</v>
       </c>
-      <c r="D145" t="str">
-        <v>ترنج بناتى (اصفر)</v>
-      </c>
-      <c r="E145" t="str">
-        <v>بيبى بنت</v>
+      <c r="D145" t="s">
+        <v>77</v>
+      </c>
+      <c r="E145" t="s">
+        <v>62</v>
       </c>
       <c r="F145">
         <v>49</v>
@@ -3299,18 +3618,18 @@
         <v>196</v>
       </c>
     </row>
-    <row r="146">
+    <row r="146" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B146">
         <v>600</v>
       </c>
       <c r="C146">
         <v>2</v>
       </c>
-      <c r="D146" t="str">
-        <v>ترنج بناتى (طوبى)</v>
-      </c>
-      <c r="E146" t="str">
-        <v>وسط بنت</v>
+      <c r="D146" t="s">
+        <v>87</v>
+      </c>
+      <c r="E146" t="s">
+        <v>88</v>
       </c>
       <c r="F146">
         <v>49.75</v>
@@ -3319,18 +3638,18 @@
         <v>199</v>
       </c>
     </row>
-    <row r="147">
+    <row r="147" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B147">
         <v>600</v>
       </c>
       <c r="C147">
         <v>3</v>
       </c>
-      <c r="D147" t="str">
-        <v>ترنج بناتى (موف)</v>
-      </c>
-      <c r="E147" t="str">
-        <v>وسط بنت</v>
+      <c r="D147" t="s">
+        <v>83</v>
+      </c>
+      <c r="E147" t="s">
+        <v>88</v>
       </c>
       <c r="F147">
         <v>50</v>
@@ -3339,18 +3658,18 @@
         <v>200</v>
       </c>
     </row>
-    <row r="148">
+    <row r="148" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B148">
         <v>600</v>
       </c>
       <c r="C148">
         <v>4</v>
       </c>
-      <c r="D148" t="str">
-        <v>ترنج بناتى (كشمير)</v>
-      </c>
-      <c r="E148" t="str">
-        <v>وسط بنت</v>
+      <c r="D148" t="s">
+        <v>89</v>
+      </c>
+      <c r="E148" t="s">
+        <v>88</v>
       </c>
       <c r="F148">
         <v>48</v>
@@ -3359,18 +3678,18 @@
         <v>192</v>
       </c>
     </row>
-    <row r="149">
+    <row r="149" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B149">
         <v>605</v>
       </c>
       <c r="C149">
         <v>8</v>
       </c>
-      <c r="D149" t="str">
-        <v>ترنج بناتى (اسود)</v>
-      </c>
-      <c r="E149" t="str">
-        <v>وسط بنت</v>
+      <c r="D149" t="s">
+        <v>90</v>
+      </c>
+      <c r="E149" t="s">
+        <v>88</v>
       </c>
       <c r="F149">
         <v>39</v>
@@ -3379,18 +3698,18 @@
         <v>156</v>
       </c>
     </row>
-    <row r="150">
+    <row r="150" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B150">
         <v>605</v>
       </c>
       <c r="C150">
         <v>11</v>
       </c>
-      <c r="D150" t="str">
-        <v>ترنج بناتى (منت)</v>
-      </c>
-      <c r="E150" t="str">
-        <v>وسط بنت</v>
+      <c r="D150" t="s">
+        <v>68</v>
+      </c>
+      <c r="E150" t="s">
+        <v>88</v>
       </c>
       <c r="F150">
         <v>40</v>
@@ -3399,18 +3718,18 @@
         <v>160</v>
       </c>
     </row>
-    <row r="151">
+    <row r="151" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B151">
         <v>605</v>
       </c>
       <c r="C151">
         <v>9</v>
       </c>
-      <c r="D151" t="str">
-        <v>ترنج بناتى (انديجو)</v>
-      </c>
-      <c r="E151" t="str">
-        <v>وسط بنت</v>
+      <c r="D151" t="s">
+        <v>61</v>
+      </c>
+      <c r="E151" t="s">
+        <v>88</v>
       </c>
       <c r="F151">
         <v>40</v>
@@ -3419,18 +3738,18 @@
         <v>160</v>
       </c>
     </row>
-    <row r="152">
+    <row r="152" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B152">
         <v>605</v>
       </c>
       <c r="C152">
         <v>10</v>
       </c>
-      <c r="D152" t="str">
-        <v>ترنج بناتى (بيج)</v>
-      </c>
-      <c r="E152" t="str">
-        <v>وسط بنت</v>
+      <c r="D152" t="s">
+        <v>91</v>
+      </c>
+      <c r="E152" t="s">
+        <v>88</v>
       </c>
       <c r="F152">
         <v>39.75</v>
@@ -3439,18 +3758,18 @@
         <v>159</v>
       </c>
     </row>
-    <row r="153">
+    <row r="153" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B153">
         <v>610</v>
       </c>
       <c r="C153">
         <v>13</v>
       </c>
-      <c r="D153" t="str">
-        <v>ترنج بناتى ( كشمير)</v>
-      </c>
-      <c r="E153" t="str">
-        <v>وسط بنت</v>
+      <c r="D153" t="s">
+        <v>92</v>
+      </c>
+      <c r="E153" t="s">
+        <v>88</v>
       </c>
       <c r="F153">
         <v>50</v>
@@ -3459,18 +3778,18 @@
         <v>200</v>
       </c>
     </row>
-    <row r="154">
+    <row r="154" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B154">
         <v>610</v>
       </c>
       <c r="C154">
         <v>12</v>
       </c>
-      <c r="D154" t="str">
-        <v>ترنج بناتى ( انديجو)</v>
-      </c>
-      <c r="E154" t="str">
-        <v>وسط بنت</v>
+      <c r="D154" t="s">
+        <v>93</v>
+      </c>
+      <c r="E154" t="s">
+        <v>88</v>
       </c>
       <c r="F154">
         <v>49.75</v>
@@ -3479,18 +3798,18 @@
         <v>199</v>
       </c>
     </row>
-    <row r="155">
+    <row r="155" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B155">
         <v>610</v>
       </c>
       <c r="C155">
         <v>14</v>
       </c>
-      <c r="D155" t="str">
-        <v>ترنج بناتى (كمونى)</v>
-      </c>
-      <c r="E155" t="str">
-        <v>وسط بنت</v>
+      <c r="D155" t="s">
+        <v>94</v>
+      </c>
+      <c r="E155" t="s">
+        <v>88</v>
       </c>
       <c r="F155">
         <v>48</v>
@@ -3499,18 +3818,18 @@
         <v>192</v>
       </c>
     </row>
-    <row r="156">
+    <row r="156" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B156">
         <v>615</v>
       </c>
       <c r="C156">
         <v>40</v>
       </c>
-      <c r="D156" t="str">
-        <v>ترنج بناتى (اسود)</v>
-      </c>
-      <c r="E156" t="str">
-        <v>وسط بنت</v>
+      <c r="D156" t="s">
+        <v>90</v>
+      </c>
+      <c r="E156" t="s">
+        <v>88</v>
       </c>
       <c r="F156">
         <v>47</v>
@@ -3519,18 +3838,18 @@
         <v>188</v>
       </c>
     </row>
-    <row r="157">
+    <row r="157" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B157">
         <v>615</v>
       </c>
       <c r="C157">
         <v>41</v>
       </c>
-      <c r="D157" t="str">
-        <v>ترنج بناتى (بيج)</v>
-      </c>
-      <c r="E157" t="str">
-        <v>وسط بنت</v>
+      <c r="D157" t="s">
+        <v>91</v>
+      </c>
+      <c r="E157" t="s">
+        <v>88</v>
       </c>
       <c r="F157">
         <v>48.75</v>
@@ -3539,18 +3858,18 @@
         <v>195</v>
       </c>
     </row>
-    <row r="158">
+    <row r="158" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B158">
         <v>615</v>
       </c>
       <c r="C158">
         <v>42</v>
       </c>
-      <c r="D158" t="str">
-        <v>ترنج بناتى (كمونى)</v>
-      </c>
-      <c r="E158" t="str">
-        <v>وسط بنت</v>
+      <c r="D158" t="s">
+        <v>94</v>
+      </c>
+      <c r="E158" t="s">
+        <v>88</v>
       </c>
       <c r="F158">
         <v>49.75</v>
@@ -3559,18 +3878,18 @@
         <v>199</v>
       </c>
     </row>
-    <row r="159">
+    <row r="159" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B159">
         <v>620</v>
       </c>
       <c r="C159">
         <v>56</v>
       </c>
-      <c r="D159" t="str">
-        <v>ترنج بناتى ( برجندى)</v>
-      </c>
-      <c r="E159" t="str">
-        <v>وسط بنت</v>
+      <c r="D159" t="s">
+        <v>95</v>
+      </c>
+      <c r="E159" t="s">
+        <v>88</v>
       </c>
       <c r="F159">
         <v>49</v>
@@ -3579,18 +3898,18 @@
         <v>196</v>
       </c>
     </row>
-    <row r="160">
+    <row r="160" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B160">
         <v>620</v>
       </c>
       <c r="C160">
         <v>57</v>
       </c>
-      <c r="D160" t="str">
-        <v>ترنج بناتى (ابيض)</v>
-      </c>
-      <c r="E160" t="str">
-        <v>وسط بنت</v>
+      <c r="D160" t="s">
+        <v>67</v>
+      </c>
+      <c r="E160" t="s">
+        <v>88</v>
       </c>
       <c r="F160">
         <v>49.75</v>
@@ -3599,18 +3918,18 @@
         <v>199</v>
       </c>
     </row>
-    <row r="161">
+    <row r="161" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B161">
         <v>620</v>
       </c>
       <c r="C161">
         <v>55</v>
       </c>
-      <c r="D161" t="str">
-        <v>ترنج بناتى (كشمير)</v>
-      </c>
-      <c r="E161" t="str">
-        <v>وسط بنت</v>
+      <c r="D161" t="s">
+        <v>89</v>
+      </c>
+      <c r="E161" t="s">
+        <v>88</v>
       </c>
       <c r="F161">
         <v>49</v>
@@ -3619,18 +3938,18 @@
         <v>196</v>
       </c>
     </row>
-    <row r="162">
+    <row r="162" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B162">
         <v>625</v>
       </c>
       <c r="C162">
         <v>52</v>
       </c>
-      <c r="D162" t="str">
-        <v>ترنج بناتى ( كافيه)</v>
-      </c>
-      <c r="E162" t="str">
-        <v>وسط بنت</v>
+      <c r="D162" t="s">
+        <v>96</v>
+      </c>
+      <c r="E162" t="s">
+        <v>88</v>
       </c>
       <c r="F162">
         <v>49</v>
@@ -3639,18 +3958,18 @@
         <v>196</v>
       </c>
     </row>
-    <row r="163">
+    <row r="163" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B163">
         <v>625</v>
       </c>
       <c r="C163">
         <v>53</v>
       </c>
-      <c r="D163" t="str">
-        <v>ترنج بناتى ( موف)</v>
-      </c>
-      <c r="E163" t="str">
-        <v>وسط بنت</v>
+      <c r="D163" t="s">
+        <v>97</v>
+      </c>
+      <c r="E163" t="s">
+        <v>88</v>
       </c>
       <c r="F163">
         <v>45.75</v>
@@ -3659,18 +3978,18 @@
         <v>183</v>
       </c>
     </row>
-    <row r="164">
+    <row r="164" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B164">
         <v>625</v>
       </c>
       <c r="C164">
         <v>54</v>
       </c>
-      <c r="D164" t="str">
-        <v>ترنج بناتى (منت)</v>
-      </c>
-      <c r="E164" t="str">
-        <v>وسط بنت</v>
+      <c r="D164" t="s">
+        <v>68</v>
+      </c>
+      <c r="E164" t="s">
+        <v>88</v>
       </c>
       <c r="F164">
         <v>50</v>
@@ -3679,18 +3998,18 @@
         <v>200</v>
       </c>
     </row>
-    <row r="165">
+    <row r="165" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B165">
         <v>630</v>
       </c>
       <c r="C165">
         <v>124</v>
       </c>
-      <c r="D165" t="str">
-        <v>ترنج بناتى (فوشيا)</v>
-      </c>
-      <c r="E165" t="str">
-        <v>وسط بنت</v>
+      <c r="D165" t="s">
+        <v>98</v>
+      </c>
+      <c r="E165" t="s">
+        <v>88</v>
       </c>
       <c r="F165">
         <v>49.75</v>
@@ -3699,18 +4018,18 @@
         <v>199</v>
       </c>
     </row>
-    <row r="166">
+    <row r="166" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B166">
         <v>630</v>
       </c>
       <c r="C166">
         <v>125</v>
       </c>
-      <c r="D166" t="str">
-        <v>ترنج بناتى (ابيض)</v>
-      </c>
-      <c r="E166" t="str">
-        <v>وسط بنت</v>
+      <c r="D166" t="s">
+        <v>67</v>
+      </c>
+      <c r="E166" t="s">
+        <v>88</v>
       </c>
       <c r="F166">
         <v>49</v>
@@ -3719,18 +4038,18 @@
         <v>196</v>
       </c>
     </row>
-    <row r="167">
+    <row r="167" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B167">
         <v>630</v>
       </c>
       <c r="C167">
         <v>126</v>
       </c>
-      <c r="D167" t="str">
-        <v>ترنج بناتى (بيج)</v>
-      </c>
-      <c r="E167" t="str">
-        <v>وسط بنت</v>
+      <c r="D167" t="s">
+        <v>91</v>
+      </c>
+      <c r="E167" t="s">
+        <v>88</v>
       </c>
       <c r="F167">
         <v>49.75</v>
@@ -3739,18 +4058,18 @@
         <v>199</v>
       </c>
     </row>
-    <row r="168">
+    <row r="168" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B168">
         <v>635</v>
       </c>
       <c r="C168">
         <v>128</v>
       </c>
-      <c r="D168" t="str">
-        <v>ترنج بناتى (روز)</v>
-      </c>
-      <c r="E168" t="str">
-        <v>وسط بنت</v>
+      <c r="D168" t="s">
+        <v>78</v>
+      </c>
+      <c r="E168" t="s">
+        <v>88</v>
       </c>
       <c r="F168">
         <v>49</v>
@@ -3759,18 +4078,18 @@
         <v>196</v>
       </c>
     </row>
-    <row r="169">
+    <row r="169" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B169">
         <v>635</v>
       </c>
       <c r="C169">
         <v>127</v>
       </c>
-      <c r="D169" t="str">
-        <v>ترنج بناتى (اكوا)</v>
-      </c>
-      <c r="E169" t="str">
-        <v>وسط بنت</v>
+      <c r="D169" t="s">
+        <v>99</v>
+      </c>
+      <c r="E169" t="s">
+        <v>88</v>
       </c>
       <c r="F169">
         <v>49</v>
@@ -3779,18 +4098,18 @@
         <v>196</v>
       </c>
     </row>
-    <row r="170">
+    <row r="170" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B170">
         <v>635</v>
       </c>
       <c r="C170">
         <v>129</v>
       </c>
-      <c r="D170" t="str">
-        <v>ترنج بناتى (بسستاج)</v>
-      </c>
-      <c r="E170" t="str">
-        <v>وسط بنت</v>
+      <c r="D170" t="s">
+        <v>100</v>
+      </c>
+      <c r="E170" t="s">
+        <v>88</v>
       </c>
       <c r="F170">
         <v>50</v>
@@ -3799,18 +4118,18 @@
         <v>200</v>
       </c>
     </row>
-    <row r="171">
+    <row r="171" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B171">
         <v>640</v>
       </c>
       <c r="C171">
         <v>137</v>
       </c>
-      <c r="D171" t="str">
-        <v>ترنج بناتى (روز)</v>
-      </c>
-      <c r="E171" t="str">
-        <v>وسط بنت</v>
+      <c r="D171" t="s">
+        <v>78</v>
+      </c>
+      <c r="E171" t="s">
+        <v>88</v>
       </c>
       <c r="F171">
         <v>50</v>
@@ -3819,18 +4138,18 @@
         <v>200</v>
       </c>
     </row>
-    <row r="172">
+    <row r="172" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B172">
         <v>640</v>
       </c>
       <c r="C172">
         <v>136</v>
       </c>
-      <c r="D172" t="str">
-        <v>ترنج بناتى(اكوا)</v>
-      </c>
-      <c r="E172" t="str">
-        <v>وسط بنت</v>
+      <c r="D172" t="s">
+        <v>101</v>
+      </c>
+      <c r="E172" t="s">
+        <v>88</v>
       </c>
       <c r="F172">
         <v>47.75</v>
@@ -3839,18 +4158,18 @@
         <v>191</v>
       </c>
     </row>
-    <row r="173">
+    <row r="173" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B173">
         <v>640</v>
       </c>
       <c r="C173">
         <v>138</v>
       </c>
-      <c r="D173" t="str">
-        <v>ترنج بناتى (سميون)</v>
-      </c>
-      <c r="E173" t="str">
-        <v>وسط بنت</v>
+      <c r="D173" t="s">
+        <v>76</v>
+      </c>
+      <c r="E173" t="s">
+        <v>88</v>
       </c>
       <c r="F173">
         <v>49</v>
@@ -3859,18 +4178,18 @@
         <v>196</v>
       </c>
     </row>
-    <row r="174">
+    <row r="174" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B174">
         <v>645</v>
       </c>
       <c r="C174">
         <v>139</v>
       </c>
-      <c r="D174" t="str">
-        <v>ترنج بناتى(برجاندى)</v>
-      </c>
-      <c r="E174" t="str">
-        <v>وسط بنت</v>
+      <c r="D174" t="s">
+        <v>102</v>
+      </c>
+      <c r="E174" t="s">
+        <v>88</v>
       </c>
       <c r="F174">
         <v>50</v>
@@ -3879,18 +4198,18 @@
         <v>200</v>
       </c>
     </row>
-    <row r="175">
+    <row r="175" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B175">
         <v>645</v>
       </c>
       <c r="C175">
         <v>141</v>
       </c>
-      <c r="D175" t="str">
-        <v>ترنج بناتى( سميون)</v>
-      </c>
-      <c r="E175" t="str">
-        <v>وسط بنت</v>
+      <c r="D175" t="s">
+        <v>103</v>
+      </c>
+      <c r="E175" t="s">
+        <v>88</v>
       </c>
       <c r="F175">
         <v>50</v>
@@ -3899,18 +4218,18 @@
         <v>200</v>
       </c>
     </row>
-    <row r="176">
+    <row r="176" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B176">
         <v>645</v>
       </c>
       <c r="C176">
         <v>140</v>
       </c>
-      <c r="D176" t="str">
-        <v>ترنج بناتى(بستاج)</v>
-      </c>
-      <c r="E176" t="str">
-        <v>وسط بنت</v>
+      <c r="D176" t="s">
+        <v>75</v>
+      </c>
+      <c r="E176" t="s">
+        <v>88</v>
       </c>
       <c r="F176">
         <v>50</v>
@@ -3919,18 +4238,18 @@
         <v>200</v>
       </c>
     </row>
-    <row r="177">
+    <row r="177" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B177">
         <v>650</v>
       </c>
       <c r="C177">
         <v>170</v>
       </c>
-      <c r="D177" t="str">
-        <v>ترنج بناتى(بستاج)</v>
-      </c>
-      <c r="E177" t="str">
-        <v>وسط بنت</v>
+      <c r="D177" t="s">
+        <v>75</v>
+      </c>
+      <c r="E177" t="s">
+        <v>88</v>
       </c>
       <c r="F177">
         <v>49.75</v>
@@ -3939,18 +4258,18 @@
         <v>199</v>
       </c>
     </row>
-    <row r="178">
+    <row r="178" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B178">
         <v>650</v>
       </c>
       <c r="C178">
         <v>171</v>
       </c>
-      <c r="D178" t="str">
-        <v>ترنج بناتى(موف)</v>
-      </c>
-      <c r="E178" t="str">
-        <v>وسط بنت</v>
+      <c r="D178" t="s">
+        <v>63</v>
+      </c>
+      <c r="E178" t="s">
+        <v>88</v>
       </c>
       <c r="F178">
         <v>49</v>
@@ -3959,18 +4278,18 @@
         <v>196</v>
       </c>
     </row>
-    <row r="179">
+    <row r="179" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B179">
         <v>650</v>
       </c>
       <c r="C179">
         <v>169</v>
       </c>
-      <c r="D179" t="str">
-        <v>ترنج بناتى(بيج)</v>
-      </c>
-      <c r="E179" t="str">
-        <v>وسط بنت</v>
+      <c r="D179" t="s">
+        <v>84</v>
+      </c>
+      <c r="E179" t="s">
+        <v>88</v>
       </c>
       <c r="F179">
         <v>49</v>
@@ -3979,18 +4298,18 @@
         <v>196</v>
       </c>
     </row>
-    <row r="180">
+    <row r="180" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B180">
         <v>660</v>
       </c>
       <c r="C180">
         <v>223</v>
       </c>
-      <c r="D180" t="str">
-        <v>ترنج بناتى (فوشيا)</v>
-      </c>
-      <c r="E180" t="str">
-        <v>وسط بنت</v>
+      <c r="D180" t="s">
+        <v>98</v>
+      </c>
+      <c r="E180" t="s">
+        <v>88</v>
       </c>
       <c r="F180">
         <v>44</v>
@@ -3999,18 +4318,18 @@
         <v>176</v>
       </c>
     </row>
-    <row r="181">
+    <row r="181" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B181">
         <v>660</v>
       </c>
       <c r="C181">
         <v>221</v>
       </c>
-      <c r="D181" t="str">
-        <v>ترنج بناتى ( اصفر)</v>
-      </c>
-      <c r="E181" t="str">
-        <v>وسط بنت</v>
+      <c r="D181" t="s">
+        <v>104</v>
+      </c>
+      <c r="E181" t="s">
+        <v>88</v>
       </c>
       <c r="F181">
         <v>35</v>
@@ -4019,21 +4338,18 @@
         <v>140</v>
       </c>
     </row>
-    <row r="182">
-      <c r="A182">
-        <v>6925</v>
-      </c>
+    <row r="182" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B182">
         <v>660</v>
       </c>
       <c r="C182">
         <v>222</v>
       </c>
-      <c r="D182" t="str">
-        <v>ترنج بناتى (روز)</v>
-      </c>
-      <c r="E182" t="str">
-        <v>وسط بنت</v>
+      <c r="D182" t="s">
+        <v>78</v>
+      </c>
+      <c r="E182" t="s">
+        <v>88</v>
       </c>
       <c r="F182">
         <v>19</v>
@@ -4042,18 +4358,18 @@
         <v>76</v>
       </c>
     </row>
-    <row r="183">
+    <row r="183" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B183">
         <v>800</v>
       </c>
       <c r="C183">
         <v>5</v>
       </c>
-      <c r="D183" t="str">
-        <v>ترنج بناتى (كمونى)</v>
-      </c>
-      <c r="E183" t="str">
-        <v>محير بنت</v>
+      <c r="D183" t="s">
+        <v>94</v>
+      </c>
+      <c r="E183" t="s">
+        <v>105</v>
       </c>
       <c r="F183">
         <v>49</v>
@@ -4062,18 +4378,18 @@
         <v>196</v>
       </c>
     </row>
-    <row r="184">
+    <row r="184" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B184">
         <v>800</v>
       </c>
       <c r="C184">
         <v>7</v>
       </c>
-      <c r="D184" t="str">
-        <v>ترنج بناتى (منت)</v>
-      </c>
-      <c r="E184" t="str">
-        <v>محير بنت</v>
+      <c r="D184" t="s">
+        <v>68</v>
+      </c>
+      <c r="E184" t="s">
+        <v>105</v>
       </c>
       <c r="F184">
         <v>49</v>
@@ -4082,18 +4398,18 @@
         <v>196</v>
       </c>
     </row>
-    <row r="185">
+    <row r="185" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B185">
         <v>800</v>
       </c>
       <c r="C185">
         <v>6</v>
       </c>
-      <c r="D185" t="str">
-        <v>ترنج بناتى ( كشمير)</v>
-      </c>
-      <c r="E185" t="str">
-        <v>محير بنت</v>
+      <c r="D185" t="s">
+        <v>92</v>
+      </c>
+      <c r="E185" t="s">
+        <v>105</v>
       </c>
       <c r="F185">
         <v>50</v>
@@ -4102,18 +4418,18 @@
         <v>200</v>
       </c>
     </row>
-    <row r="186">
+    <row r="186" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B186">
         <v>805</v>
       </c>
       <c r="C186">
         <v>18</v>
       </c>
-      <c r="D186" t="str">
-        <v>ترنج بناتى ( كافيه)</v>
-      </c>
-      <c r="E186" t="str">
-        <v>محير بنت</v>
+      <c r="D186" t="s">
+        <v>96</v>
+      </c>
+      <c r="E186" t="s">
+        <v>105</v>
       </c>
       <c r="F186">
         <v>40</v>
@@ -4122,18 +4438,18 @@
         <v>160</v>
       </c>
     </row>
-    <row r="187">
+    <row r="187" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B187">
         <v>805</v>
       </c>
       <c r="C187">
         <v>15</v>
       </c>
-      <c r="D187" t="str">
-        <v>ترنج بناتى (اوف ويت)</v>
-      </c>
-      <c r="E187" t="str">
-        <v>محير بنت</v>
+      <c r="D187" t="s">
+        <v>70</v>
+      </c>
+      <c r="E187" t="s">
+        <v>105</v>
       </c>
       <c r="F187">
         <v>40</v>
@@ -4142,18 +4458,18 @@
         <v>160</v>
       </c>
     </row>
-    <row r="188">
+    <row r="188" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B188">
         <v>805</v>
       </c>
       <c r="C188">
         <v>16</v>
       </c>
-      <c r="D188" t="str">
-        <v>ترنج بناتى (رمادى)</v>
-      </c>
-      <c r="E188" t="str">
-        <v>محير بنت</v>
+      <c r="D188" t="s">
+        <v>106</v>
+      </c>
+      <c r="E188" t="s">
+        <v>105</v>
       </c>
       <c r="F188">
         <v>40</v>
@@ -4162,18 +4478,18 @@
         <v>160</v>
       </c>
     </row>
-    <row r="189">
+    <row r="189" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B189">
         <v>805</v>
       </c>
       <c r="C189">
         <v>17</v>
       </c>
-      <c r="D189" t="str">
-        <v>ترنج بناتى (كشمير)</v>
-      </c>
-      <c r="E189" t="str">
-        <v>محير بنت</v>
+      <c r="D189" t="s">
+        <v>89</v>
+      </c>
+      <c r="E189" t="s">
+        <v>105</v>
       </c>
       <c r="F189">
         <v>39.75</v>
@@ -4182,18 +4498,18 @@
         <v>159</v>
       </c>
     </row>
-    <row r="190">
+    <row r="190" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B190">
         <v>810</v>
       </c>
       <c r="C190">
         <v>19</v>
       </c>
-      <c r="D190" t="str">
-        <v>ترنج بناتى ( انديجو)</v>
-      </c>
-      <c r="E190" t="str">
-        <v>محير بنت</v>
+      <c r="D190" t="s">
+        <v>93</v>
+      </c>
+      <c r="E190" t="s">
+        <v>105</v>
       </c>
       <c r="F190">
         <v>49</v>
@@ -4202,18 +4518,18 @@
         <v>196</v>
       </c>
     </row>
-    <row r="191">
+    <row r="191" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B191">
         <v>810</v>
       </c>
       <c r="C191">
         <v>21</v>
       </c>
-      <c r="D191" t="str">
-        <v>ترنج بناتى (موف)</v>
-      </c>
-      <c r="E191" t="str">
-        <v>محير بنت</v>
+      <c r="D191" t="s">
+        <v>83</v>
+      </c>
+      <c r="E191" t="s">
+        <v>105</v>
       </c>
       <c r="F191">
         <v>50</v>
@@ -4222,18 +4538,18 @@
         <v>200</v>
       </c>
     </row>
-    <row r="192">
+    <row r="192" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B192">
         <v>810</v>
       </c>
       <c r="C192">
         <v>20</v>
       </c>
-      <c r="D192" t="str">
-        <v>ترنج بناتى (برجاندى)</v>
-      </c>
-      <c r="E192" t="str">
-        <v>محير بنت</v>
+      <c r="D192" t="s">
+        <v>69</v>
+      </c>
+      <c r="E192" t="s">
+        <v>105</v>
       </c>
       <c r="F192">
         <v>49</v>
@@ -4242,18 +4558,18 @@
         <v>196</v>
       </c>
     </row>
-    <row r="193">
+    <row r="193" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B193">
         <v>815</v>
       </c>
       <c r="C193">
         <v>38</v>
       </c>
-      <c r="D193" t="str">
-        <v>ترنج بناتى (اسود)</v>
-      </c>
-      <c r="E193" t="str">
-        <v>محير بنت</v>
+      <c r="D193" t="s">
+        <v>90</v>
+      </c>
+      <c r="E193" t="s">
+        <v>105</v>
       </c>
       <c r="F193">
         <v>50</v>
@@ -4262,18 +4578,18 @@
         <v>200</v>
       </c>
     </row>
-    <row r="194">
+    <row r="194" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B194">
         <v>815</v>
       </c>
       <c r="C194">
         <v>39</v>
       </c>
-      <c r="D194" t="str">
-        <v>ترنج بناتى(موف)</v>
-      </c>
-      <c r="E194" t="str">
-        <v>محير بنت</v>
+      <c r="D194" t="s">
+        <v>63</v>
+      </c>
+      <c r="E194" t="s">
+        <v>105</v>
       </c>
       <c r="F194">
         <v>49.5</v>
@@ -4282,18 +4598,18 @@
         <v>198</v>
       </c>
     </row>
-    <row r="195">
+    <row r="195" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B195">
         <v>815</v>
       </c>
       <c r="C195">
         <v>37</v>
       </c>
-      <c r="D195" t="str">
-        <v>ترنج بناتى ( كافيه)</v>
-      </c>
-      <c r="E195" t="str">
-        <v>محير بنت</v>
+      <c r="D195" t="s">
+        <v>96</v>
+      </c>
+      <c r="E195" t="s">
+        <v>105</v>
       </c>
       <c r="F195">
         <v>49.75</v>
@@ -4302,18 +4618,18 @@
         <v>199</v>
       </c>
     </row>
-    <row r="196">
+    <row r="196" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B196">
         <v>820</v>
       </c>
       <c r="C196">
         <v>44</v>
       </c>
-      <c r="D196" t="str">
-        <v>ترنج بناتى (انديجو)</v>
-      </c>
-      <c r="E196" t="str">
-        <v>محير بنت</v>
+      <c r="D196" t="s">
+        <v>61</v>
+      </c>
+      <c r="E196" t="s">
+        <v>105</v>
       </c>
       <c r="F196">
         <v>49.75</v>
@@ -4322,18 +4638,18 @@
         <v>199</v>
       </c>
     </row>
-    <row r="197">
+    <row r="197" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B197">
         <v>820</v>
       </c>
       <c r="C197">
         <v>43</v>
       </c>
-      <c r="D197" t="str">
-        <v>ترنج بناتى ( ابيض)</v>
-      </c>
-      <c r="E197" t="str">
-        <v>محير بنت</v>
+      <c r="D197" t="s">
+        <v>107</v>
+      </c>
+      <c r="E197" t="s">
+        <v>105</v>
       </c>
       <c r="F197">
         <v>49</v>
@@ -4342,18 +4658,18 @@
         <v>196</v>
       </c>
     </row>
-    <row r="198">
+    <row r="198" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B198">
         <v>820</v>
       </c>
       <c r="C198">
         <v>45</v>
       </c>
-      <c r="D198" t="str">
-        <v>ترنج بناتى ( كمونى)</v>
-      </c>
-      <c r="E198" t="str">
-        <v>محير بنت</v>
+      <c r="D198" t="s">
+        <v>108</v>
+      </c>
+      <c r="E198" t="s">
+        <v>105</v>
       </c>
       <c r="F198">
         <v>45</v>
@@ -4362,18 +4678,18 @@
         <v>180</v>
       </c>
     </row>
-    <row r="199">
+    <row r="199" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B199">
         <v>825</v>
       </c>
       <c r="C199">
         <v>46</v>
       </c>
-      <c r="D199" t="str">
-        <v>ترنج بناتى (كشمير)</v>
-      </c>
-      <c r="E199" t="str">
-        <v>محير بنت</v>
+      <c r="D199" t="s">
+        <v>89</v>
+      </c>
+      <c r="E199" t="s">
+        <v>105</v>
       </c>
       <c r="F199">
         <v>48</v>
@@ -4382,18 +4698,18 @@
         <v>192</v>
       </c>
     </row>
-    <row r="200">
+    <row r="200" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B200">
         <v>825</v>
       </c>
       <c r="C200">
         <v>48</v>
       </c>
-      <c r="D200" t="str">
-        <v>ترنج بناتى (اسود)</v>
-      </c>
-      <c r="E200" t="str">
-        <v>محير بنت</v>
+      <c r="D200" t="s">
+        <v>90</v>
+      </c>
+      <c r="E200" t="s">
+        <v>105</v>
       </c>
       <c r="F200">
         <v>49</v>
@@ -4402,18 +4718,18 @@
         <v>196</v>
       </c>
     </row>
-    <row r="201">
+    <row r="201" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B201">
         <v>825</v>
       </c>
       <c r="C201">
         <v>47</v>
       </c>
-      <c r="D201" t="str">
-        <v>ترنج بناتى (بيج)</v>
-      </c>
-      <c r="E201" t="str">
-        <v>محير بنت</v>
+      <c r="D201" t="s">
+        <v>91</v>
+      </c>
+      <c r="E201" t="s">
+        <v>105</v>
       </c>
       <c r="F201">
         <v>49</v>
@@ -4422,18 +4738,18 @@
         <v>196</v>
       </c>
     </row>
-    <row r="202">
+    <row r="202" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B202">
         <v>830</v>
       </c>
       <c r="C202">
         <v>120</v>
       </c>
-      <c r="D202" t="str">
-        <v>ترنج بناتى (برجاندى)</v>
-      </c>
-      <c r="E202" t="str">
-        <v>محير بنت</v>
+      <c r="D202" t="s">
+        <v>69</v>
+      </c>
+      <c r="E202" t="s">
+        <v>105</v>
       </c>
       <c r="F202">
         <v>49</v>
@@ -4442,18 +4758,18 @@
         <v>196</v>
       </c>
     </row>
-    <row r="203">
+    <row r="203" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B203">
         <v>830</v>
       </c>
       <c r="C203">
         <v>118</v>
       </c>
-      <c r="D203" t="str">
-        <v>ترنج بناتى (اكوا)</v>
-      </c>
-      <c r="E203" t="str">
-        <v>محير بنت</v>
+      <c r="D203" t="s">
+        <v>99</v>
+      </c>
+      <c r="E203" t="s">
+        <v>105</v>
       </c>
       <c r="F203">
         <v>49</v>
@@ -4462,18 +4778,18 @@
         <v>196</v>
       </c>
     </row>
-    <row r="204">
+    <row r="204" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B204">
         <v>830</v>
       </c>
       <c r="C204">
         <v>119</v>
       </c>
-      <c r="D204" t="str">
-        <v>ترنج بناتى (روز)</v>
-      </c>
-      <c r="E204" t="str">
-        <v>محير بنت</v>
+      <c r="D204" t="s">
+        <v>78</v>
+      </c>
+      <c r="E204" t="s">
+        <v>105</v>
       </c>
       <c r="F204">
         <v>49</v>
@@ -4482,18 +4798,18 @@
         <v>196</v>
       </c>
     </row>
-    <row r="205">
+    <row r="205" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B205">
         <v>835</v>
       </c>
       <c r="C205">
         <v>122</v>
       </c>
-      <c r="D205" t="str">
-        <v>ترنج بناتى (سميون)</v>
-      </c>
-      <c r="E205" t="str">
-        <v>محير بنت</v>
+      <c r="D205" t="s">
+        <v>76</v>
+      </c>
+      <c r="E205" t="s">
+        <v>105</v>
       </c>
       <c r="F205">
         <v>50</v>
@@ -4502,18 +4818,18 @@
         <v>200</v>
       </c>
     </row>
-    <row r="206">
+    <row r="206" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B206">
         <v>835</v>
       </c>
       <c r="C206">
         <v>123</v>
       </c>
-      <c r="D206" t="str">
-        <v>ترنج بناتى (ابيض)</v>
-      </c>
-      <c r="E206" t="str">
-        <v>محير بنت</v>
+      <c r="D206" t="s">
+        <v>67</v>
+      </c>
+      <c r="E206" t="s">
+        <v>105</v>
       </c>
       <c r="F206">
         <v>49</v>
@@ -4522,18 +4838,18 @@
         <v>196</v>
       </c>
     </row>
-    <row r="207">
+    <row r="207" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B207">
         <v>835</v>
       </c>
       <c r="C207">
         <v>121</v>
       </c>
-      <c r="D207" t="str">
-        <v>ترنج بناتى ( موف)</v>
-      </c>
-      <c r="E207" t="str">
-        <v>محير بنت</v>
+      <c r="D207" t="s">
+        <v>97</v>
+      </c>
+      <c r="E207" t="s">
+        <v>105</v>
       </c>
       <c r="F207">
         <v>48.75</v>
@@ -4542,18 +4858,18 @@
         <v>195</v>
       </c>
     </row>
-    <row r="208">
+    <row r="208" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B208">
         <v>840</v>
       </c>
       <c r="C208">
         <v>132</v>
       </c>
-      <c r="D208" t="str">
-        <v>ترنج بناتى (فوشيا)</v>
-      </c>
-      <c r="E208" t="str">
-        <v>محير بنت</v>
+      <c r="D208" t="s">
+        <v>98</v>
+      </c>
+      <c r="E208" t="s">
+        <v>105</v>
       </c>
       <c r="F208">
         <v>46</v>
@@ -4562,18 +4878,18 @@
         <v>184</v>
       </c>
     </row>
-    <row r="209">
+    <row r="209" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B209">
         <v>840</v>
       </c>
       <c r="C209">
         <v>131</v>
       </c>
-      <c r="D209" t="str">
-        <v>ترنج بناتى (اصفر)</v>
-      </c>
-      <c r="E209" t="str">
-        <v>محير بنت</v>
+      <c r="D209" t="s">
+        <v>77</v>
+      </c>
+      <c r="E209" t="s">
+        <v>105</v>
       </c>
       <c r="F209">
         <v>49.75</v>
@@ -4582,18 +4898,18 @@
         <v>199</v>
       </c>
     </row>
-    <row r="210">
+    <row r="210" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B210">
         <v>840</v>
       </c>
       <c r="C210">
         <v>130</v>
       </c>
-      <c r="D210" t="str">
-        <v>ترنج بناتى (موف)</v>
-      </c>
-      <c r="E210" t="str">
-        <v>محير بنت</v>
+      <c r="D210" t="s">
+        <v>83</v>
+      </c>
+      <c r="E210" t="s">
+        <v>105</v>
       </c>
       <c r="F210">
         <v>49</v>
@@ -4602,18 +4918,18 @@
         <v>196</v>
       </c>
     </row>
-    <row r="211">
+    <row r="211" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B211">
         <v>845</v>
       </c>
       <c r="C211">
         <v>135</v>
       </c>
-      <c r="D211" t="str">
-        <v>ترنج بناتى(فوشيا)</v>
-      </c>
-      <c r="E211" t="str">
-        <v>محير بنت</v>
+      <c r="D211" t="s">
+        <v>74</v>
+      </c>
+      <c r="E211" t="s">
+        <v>105</v>
       </c>
       <c r="F211">
         <v>49</v>
@@ -4622,18 +4938,18 @@
         <v>196</v>
       </c>
     </row>
-    <row r="212">
+    <row r="212" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B212">
         <v>845</v>
       </c>
       <c r="C212">
         <v>134</v>
       </c>
-      <c r="D212" t="str">
-        <v>ترنج بناتى( ابيض)</v>
-      </c>
-      <c r="E212" t="str">
-        <v>محير بنت</v>
+      <c r="D212" t="s">
+        <v>109</v>
+      </c>
+      <c r="E212" t="s">
+        <v>105</v>
       </c>
       <c r="F212">
         <v>43</v>
@@ -4642,18 +4958,18 @@
         <v>172</v>
       </c>
     </row>
-    <row r="213">
+    <row r="213" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B213">
         <v>845</v>
       </c>
       <c r="C213">
         <v>133</v>
       </c>
-      <c r="D213" t="str">
-        <v>ترنج بناتى(اكوا)</v>
-      </c>
-      <c r="E213" t="str">
-        <v>محير بنت</v>
+      <c r="D213" t="s">
+        <v>101</v>
+      </c>
+      <c r="E213" t="s">
+        <v>105</v>
       </c>
       <c r="F213">
         <v>47</v>
@@ -4662,18 +4978,18 @@
         <v>188</v>
       </c>
     </row>
-    <row r="214">
+    <row r="214" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B214">
         <v>850</v>
       </c>
       <c r="C214">
         <v>165</v>
       </c>
-      <c r="D214" t="str">
-        <v>ترنج بناتى(اكوا)</v>
-      </c>
-      <c r="E214" t="str">
-        <v>محير بنت</v>
+      <c r="D214" t="s">
+        <v>101</v>
+      </c>
+      <c r="E214" t="s">
+        <v>105</v>
       </c>
       <c r="F214">
         <v>34</v>
@@ -4682,18 +4998,18 @@
         <v>136</v>
       </c>
     </row>
-    <row r="215">
+    <row r="215" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B215">
         <v>850</v>
       </c>
       <c r="C215">
         <v>168</v>
       </c>
-      <c r="D215" t="str">
-        <v>ترنج بناتى (روز)</v>
-      </c>
-      <c r="E215" t="str">
-        <v>محير بنت</v>
+      <c r="D215" t="s">
+        <v>78</v>
+      </c>
+      <c r="E215" t="s">
+        <v>105</v>
       </c>
       <c r="F215">
         <v>47.75</v>
@@ -4702,18 +5018,18 @@
         <v>191</v>
       </c>
     </row>
-    <row r="216">
+    <row r="216" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B216">
         <v>850</v>
       </c>
       <c r="C216">
         <v>167</v>
       </c>
-      <c r="D216" t="str">
-        <v>ترنج بناتى( بستاج)</v>
-      </c>
-      <c r="E216" t="str">
-        <v>محير بنت</v>
+      <c r="D216" t="s">
+        <v>110</v>
+      </c>
+      <c r="E216" t="s">
+        <v>105</v>
       </c>
       <c r="F216">
         <v>13.75</v>
@@ -4722,21 +5038,18 @@
         <v>55</v>
       </c>
     </row>
-    <row r="217">
-      <c r="A217">
-        <v>6451</v>
-      </c>
+    <row r="217" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B217">
         <v>850</v>
       </c>
       <c r="C217">
         <v>166</v>
       </c>
-      <c r="D217" t="str">
-        <v>ترنج بناتى ( ابيض)</v>
-      </c>
-      <c r="E217" t="str">
-        <v>محير بنت</v>
+      <c r="D217" t="s">
+        <v>107</v>
+      </c>
+      <c r="E217" t="s">
+        <v>105</v>
       </c>
       <c r="F217">
         <v>44</v>
@@ -4745,18 +5058,18 @@
         <v>176</v>
       </c>
     </row>
-    <row r="218">
+    <row r="218" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B218">
         <v>5030</v>
       </c>
       <c r="C218">
         <v>444</v>
       </c>
-      <c r="D218" t="str">
-        <v>سوت وسط حوض (فوشيا)</v>
-      </c>
-      <c r="E218" t="str">
-        <v/>
+      <c r="D218" t="s">
+        <v>111</v>
+      </c>
+      <c r="E218" t="s">
+        <v>112</v>
       </c>
       <c r="F218">
         <v>0</v>
@@ -4765,18 +5078,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219">
+    <row r="219" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B219">
         <v>5030</v>
       </c>
       <c r="C219">
         <v>442</v>
       </c>
-      <c r="D219" t="str">
-        <v>سوت وسط حوض (اسود)</v>
-      </c>
-      <c r="E219" t="str">
-        <v>بناتي</v>
+      <c r="D219" t="s">
+        <v>113</v>
+      </c>
+      <c r="E219" t="s">
+        <v>114</v>
       </c>
       <c r="F219">
         <v>0</v>
@@ -4785,18 +5098,18 @@
         <v>0</v>
       </c>
     </row>
-    <row r="220">
+    <row r="220" spans="2:7" ht="15.6" x14ac:dyDescent="0.3">
       <c r="B220">
         <v>5030</v>
       </c>
       <c r="C220">
         <v>443</v>
       </c>
-      <c r="D220" t="str">
-        <v>سوت وسط حوض (بني فاتح)</v>
-      </c>
-      <c r="E220" t="str">
-        <v>بناتي</v>
+      <c r="D220" t="s">
+        <v>115</v>
+      </c>
+      <c r="E220" t="s">
+        <v>114</v>
       </c>
       <c r="F220">
         <v>0</v>
@@ -4806,8 +5119,9 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:G220"/>
+    <ignoredError sqref="B1:G220" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
 </file>